--- a/mlb_weather_professional_v5_2026_07_25.xlsx
+++ b/mlb_weather_professional_v5_2026_07_25.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="394">
   <si>
     <t>Date</t>
   </si>
@@ -587,15 +587,15 @@
     <t>🟢 Good</t>
   </si>
   <si>
+    <t>WORSENING</t>
+  </si>
+  <si>
+    <t>IMPROVING RAPIDLY</t>
+  </si>
+  <si>
     <t>WORSENING RAPIDLY</t>
   </si>
   <si>
-    <t>WORSENING</t>
-  </si>
-  <si>
-    <t>IMPROVING RAPIDLY</t>
-  </si>
-  <si>
     <t>IMPROVING</t>
   </si>
   <si>
@@ -611,43 +611,49 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-07-24 06:10:54 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:10:55 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:10:56 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:10:58 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:10:59 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:11:00 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:11:02 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:11:03 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:11:04 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:11:05 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:11:06 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:11:08 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:11:10 PM PDT</t>
+    <t>2026-07-24 06:17:13 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:14 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:15 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:16 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:17 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:19 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:20 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:22 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:23 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:24 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:25 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:26 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:27 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:29 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:17:30 PM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -1022,43 +1028,49 @@
     <t>09:15 PM CDT</t>
   </si>
   <si>
-    <t>2026-07-25 01:10:54 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:10:55 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:10:56 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:10:58 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:10:59 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:11:00 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:11:02 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:11:03 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:11:04 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:11:05 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:11:06 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:11:08 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:11:10 UTC</t>
+    <t>2026-07-25 01:17:13 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:14 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:15 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:16 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:17 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:19 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:20 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:22 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:23 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:24 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:25 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:26 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:27 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:29 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:17:30 UTC</t>
   </si>
   <si>
     <t>2026-07-24T20:24:19+00:00</t>
@@ -1976,7 +1988,7 @@
         <v>188</v>
       </c>
       <c r="AR2">
-        <v>-4.3</v>
+        <v>-3.7</v>
       </c>
       <c r="AS2">
         <v>0</v>
@@ -2000,7 +2012,7 @@
         <v>196</v>
       </c>
       <c r="AZ2">
-        <v>286.6</v>
+        <v>292.9</v>
       </c>
       <c r="BA2">
         <v>5</v>
@@ -2131,10 +2143,10 @@
         <v>41.2</v>
       </c>
       <c r="AQ3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AR3">
-        <v>-1.8</v>
+        <v>-2.2</v>
       </c>
       <c r="AS3">
         <v>0</v>
@@ -2158,7 +2170,7 @@
         <v>197</v>
       </c>
       <c r="AZ3">
-        <v>77.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2289,7 +2301,7 @@
         <v>75.40000000000001</v>
       </c>
       <c r="AQ4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AR4">
         <v>7.5</v>
@@ -2316,7 +2328,7 @@
         <v>198</v>
       </c>
       <c r="AZ4">
-        <v>285</v>
+        <v>291.3</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2447,10 +2459,10 @@
         <v>41.5</v>
       </c>
       <c r="AQ5" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AR5">
-        <v>-6.1</v>
+        <v>-5.9</v>
       </c>
       <c r="AS5">
         <v>0</v>
@@ -2474,7 +2486,7 @@
         <v>199</v>
       </c>
       <c r="AZ5">
-        <v>160.2</v>
+        <v>166.5</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2629,10 +2641,10 @@
         <v>27.2</v>
       </c>
       <c r="AY6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AZ6">
-        <v>293.4</v>
+        <v>299.7</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2766,7 +2778,7 @@
         <v>192</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AS7">
         <v>0</v>
@@ -2787,10 +2799,10 @@
         <v>13.4</v>
       </c>
       <c r="AY7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AZ7">
-        <v>286.8</v>
+        <v>293.2</v>
       </c>
       <c r="BA7">
         <v>5</v>
@@ -2945,10 +2957,10 @@
         <v>12.2</v>
       </c>
       <c r="AY8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AZ8">
-        <v>369.6</v>
+        <v>376</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -3082,7 +3094,7 @@
         <v>192</v>
       </c>
       <c r="AR9">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AS9">
         <v>0</v>
@@ -3103,10 +3115,10 @@
         <v>5.7</v>
       </c>
       <c r="AY9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AZ9">
-        <v>144.2</v>
+        <v>150.5</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3261,10 +3273,10 @@
         <v>6.7</v>
       </c>
       <c r="AY10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AZ10">
-        <v>77.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3398,7 +3410,7 @@
         <v>191</v>
       </c>
       <c r="AR11">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AS11">
         <v>0</v>
@@ -3419,10 +3431,10 @@
         <v>10.2</v>
       </c>
       <c r="AY11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AZ11">
-        <v>94.7</v>
+        <v>101</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3556,7 +3568,7 @@
         <v>192</v>
       </c>
       <c r="AR12">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="AS12">
         <v>0</v>
@@ -3577,10 +3589,10 @@
         <v>14.1</v>
       </c>
       <c r="AY12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AZ12">
-        <v>324.7</v>
+        <v>331</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3714,7 +3726,7 @@
         <v>192</v>
       </c>
       <c r="AR13">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AS13">
         <v>0</v>
@@ -3735,10 +3747,10 @@
         <v>7.5</v>
       </c>
       <c r="AY13" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AZ13">
-        <v>89.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3869,10 +3881,10 @@
         <v>46.7</v>
       </c>
       <c r="AQ14" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AR14">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AS14">
         <v>0</v>
@@ -3890,13 +3902,13 @@
         <v>193</v>
       </c>
       <c r="AX14">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="AY14" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AZ14">
-        <v>381</v>
+        <v>387.3</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -4027,10 +4039,10 @@
         <v>68.90000000000001</v>
       </c>
       <c r="AQ15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="AR15">
-        <v>-0.8</v>
+        <v>-1.6</v>
       </c>
       <c r="AS15">
         <v>0</v>
@@ -4048,13 +4060,13 @@
         <v>193</v>
       </c>
       <c r="AX15">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="AY15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AZ15">
-        <v>29.8</v>
+        <v>36.2</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4209,10 +4221,10 @@
         <v>9.4</v>
       </c>
       <c r="AY16" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AZ16">
-        <v>119.1</v>
+        <v>125.4</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4353,286 +4365,286 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AZ1" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="BC1" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BF1" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="BG1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="BH1" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="BI1" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="BJ1" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="BK1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="BL1" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="BM1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="BN1" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="BO1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="BP1" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="BQ1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="BR1" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="BS1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="BT1" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="BU1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="BV1" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="BW1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="BX1" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="BY1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="BZ1" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="CA1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="CB1" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="CC1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="CD1" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="CE1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="CF1" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="CG1" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="CH1" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="CI1" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="CJ1" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="CK1" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="CL1" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="CM1" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="CN1" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="CO1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="CP1" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="CQ1" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="CR1" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="CS1" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="CT1" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="CU1" s="1" t="s">
         <v>49</v>
@@ -4641,16 +4653,16 @@
         <v>48</v>
       </c>
       <c r="CW1" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="CX1" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="CY1" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="CZ1" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:104">
@@ -4667,25 +4679,25 @@
         <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F2" t="s">
         <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H2" t="s">
         <v>196</v>
       </c>
       <c r="I2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J2">
-        <v>286.6</v>
+        <v>292.9</v>
       </c>
       <c r="K2">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="L2">
         <v>5</v>
@@ -4712,13 +4724,13 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="V2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="W2">
         <v>0.1667</v>
@@ -4808,10 +4820,10 @@
         <v>237</v>
       </c>
       <c r="AZ2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB2">
         <v>96</v>
@@ -4898,7 +4910,7 @@
         <v>1.1468</v>
       </c>
       <c r="CD2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE2">
         <v>2100</v>
@@ -4981,25 +4993,25 @@
         <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H3" t="s">
         <v>196</v>
       </c>
       <c r="I3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J3">
-        <v>286.6</v>
+        <v>292.9</v>
       </c>
       <c r="K3">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -5026,13 +5038,13 @@
         <v>100</v>
       </c>
       <c r="T3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U3" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="V3" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="W3">
         <v>0.1667</v>
@@ -5122,10 +5134,10 @@
         <v>215.3</v>
       </c>
       <c r="AZ3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB3">
         <v>93.3</v>
@@ -5212,7 +5224,7 @@
         <v>1.1421</v>
       </c>
       <c r="CD3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE3">
         <v>2250</v>
@@ -5295,25 +5307,25 @@
         <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F4" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="G4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H4" t="s">
         <v>196</v>
       </c>
       <c r="I4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J4">
-        <v>286.6</v>
+        <v>292.9</v>
       </c>
       <c r="K4">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -5340,13 +5352,13 @@
         <v>81.2</v>
       </c>
       <c r="T4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="V4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="W4">
         <v>0.1667</v>
@@ -5436,10 +5448,10 @@
         <v>210.5</v>
       </c>
       <c r="AZ4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB4">
         <v>91.59999999999999</v>
@@ -5526,7 +5538,7 @@
         <v>1.1398</v>
       </c>
       <c r="CD4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE4">
         <v>2320</v>
@@ -5609,25 +5621,25 @@
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F5" t="s">
         <v>111</v>
       </c>
       <c r="G5" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H5" t="s">
         <v>196</v>
       </c>
       <c r="I5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J5">
-        <v>286.6</v>
+        <v>292.9</v>
       </c>
       <c r="K5">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -5654,13 +5666,13 @@
         <v>100</v>
       </c>
       <c r="T5" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="V5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="W5">
         <v>0.1667</v>
@@ -5750,10 +5762,10 @@
         <v>206.2</v>
       </c>
       <c r="AZ5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB5">
         <v>89.7</v>
@@ -5840,7 +5852,7 @@
         <v>1.138</v>
       </c>
       <c r="CD5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE5">
         <v>2369</v>
@@ -5923,25 +5935,25 @@
         <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F6" t="s">
         <v>109</v>
       </c>
       <c r="G6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H6" t="s">
         <v>197</v>
       </c>
       <c r="I6" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J6">
-        <v>77.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K6">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -5968,13 +5980,13 @@
         <v>81.2</v>
       </c>
       <c r="T6" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U6" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="V6" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="W6">
         <v>0.0833</v>
@@ -6064,10 +6076,10 @@
         <v>91.5</v>
       </c>
       <c r="AZ6" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA6" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB6">
         <v>90</v>
@@ -6154,7 +6166,7 @@
         <v>1.1581</v>
       </c>
       <c r="CD6" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE6">
         <v>1752</v>
@@ -6237,25 +6249,25 @@
         <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="G7" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H7" t="s">
         <v>197</v>
       </c>
       <c r="I7" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J7">
-        <v>77.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K7">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -6282,13 +6294,13 @@
         <v>81.2</v>
       </c>
       <c r="T7" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U7" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="V7" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="W7">
         <v>0.0833</v>
@@ -6378,10 +6390,10 @@
         <v>91.09999999999999</v>
       </c>
       <c r="AZ7" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA7" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB7">
         <v>84.90000000000001</v>
@@ -6468,7 +6480,7 @@
         <v>1.1575</v>
       </c>
       <c r="CD7" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE7">
         <v>1774</v>
@@ -6551,25 +6563,25 @@
         <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F8" t="s">
         <v>112</v>
       </c>
       <c r="G8" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H8" t="s">
         <v>197</v>
       </c>
       <c r="I8" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J8">
-        <v>77.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K8">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -6596,13 +6608,13 @@
         <v>81.2</v>
       </c>
       <c r="T8" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U8" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V8" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W8">
         <v>0.0833</v>
@@ -6692,10 +6704,10 @@
         <v>93.7</v>
       </c>
       <c r="AZ8" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA8" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB8">
         <v>90.5</v>
@@ -6782,7 +6794,7 @@
         <v>1.1591</v>
       </c>
       <c r="CD8" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE8">
         <v>1723</v>
@@ -6865,25 +6877,25 @@
         <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F9" t="s">
         <v>115</v>
       </c>
       <c r="G9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="H9" t="s">
         <v>197</v>
       </c>
       <c r="I9" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J9">
-        <v>77.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K9">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -6910,13 +6922,13 @@
         <v>56.2</v>
       </c>
       <c r="T9" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U9" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V9" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W9">
         <v>0.0833</v>
@@ -7006,10 +7018,10 @@
         <v>96.59999999999999</v>
       </c>
       <c r="AZ9" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA9" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB9">
         <v>92.3</v>
@@ -7096,7 +7108,7 @@
         <v>1.1631</v>
       </c>
       <c r="CD9" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE9">
         <v>1594</v>
@@ -7179,25 +7191,25 @@
         <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F10" t="s">
         <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H10" t="s">
         <v>198</v>
       </c>
       <c r="I10" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J10">
-        <v>285</v>
+        <v>291.3</v>
       </c>
       <c r="K10">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -7224,13 +7236,13 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U10" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="V10" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="W10">
         <v>0.0833</v>
@@ -7320,10 +7332,10 @@
         <v>275.2</v>
       </c>
       <c r="AZ10" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BA10" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BB10">
         <v>86.09999999999999</v>
@@ -7410,7 +7422,7 @@
         <v>1.2186</v>
       </c>
       <c r="CD10" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE10">
         <v>-8</v>
@@ -7493,25 +7505,25 @@
         <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H11" t="s">
         <v>198</v>
       </c>
       <c r="I11" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J11">
-        <v>285</v>
+        <v>291.3</v>
       </c>
       <c r="K11">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -7538,13 +7550,13 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="V11" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="W11">
         <v>0.0833</v>
@@ -7634,10 +7646,10 @@
         <v>274.8</v>
       </c>
       <c r="AZ11" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BA11" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BB11">
         <v>85.3</v>
@@ -7724,7 +7736,7 @@
         <v>1.2185</v>
       </c>
       <c r="CD11" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE11">
         <v>-4</v>
@@ -7807,25 +7819,25 @@
         <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="G12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H12" t="s">
         <v>198</v>
       </c>
       <c r="I12" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J12">
-        <v>285</v>
+        <v>291.3</v>
       </c>
       <c r="K12">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -7852,13 +7864,13 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U12" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="V12" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="W12">
         <v>0.0833</v>
@@ -7948,10 +7960,10 @@
         <v>274.8</v>
       </c>
       <c r="AZ12" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BA12" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BB12">
         <v>85.7</v>
@@ -8038,7 +8050,7 @@
         <v>1.217</v>
       </c>
       <c r="CD12" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE12">
         <v>38</v>
@@ -8121,25 +8133,25 @@
         <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="G13" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H13" t="s">
         <v>198</v>
       </c>
       <c r="I13" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J13">
-        <v>285</v>
+        <v>291.3</v>
       </c>
       <c r="K13">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -8166,13 +8178,13 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U13" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="V13" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="W13">
         <v>0.0833</v>
@@ -8262,10 +8274,10 @@
         <v>274.6</v>
       </c>
       <c r="AZ13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BA13" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BB13">
         <v>85.3</v>
@@ -8352,7 +8364,7 @@
         <v>1.2175</v>
       </c>
       <c r="CD13" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE13">
         <v>22</v>
@@ -8435,25 +8447,25 @@
         <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F14" t="s">
         <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H14" t="s">
         <v>199</v>
       </c>
       <c r="I14" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J14">
-        <v>160.2</v>
+        <v>166.5</v>
       </c>
       <c r="K14">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -8480,13 +8492,13 @@
         <v>100</v>
       </c>
       <c r="T14" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U14" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="V14" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="W14">
         <v>0.1667</v>
@@ -8576,10 +8588,10 @@
         <v>90.8</v>
       </c>
       <c r="AZ14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA14" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB14">
         <v>91.5</v>
@@ -8666,7 +8678,7 @@
         <v>1.1798</v>
       </c>
       <c r="CD14" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE14">
         <v>1156</v>
@@ -8749,25 +8761,25 @@
         <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F15" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G15" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H15" t="s">
         <v>199</v>
       </c>
       <c r="I15" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J15">
-        <v>160.2</v>
+        <v>166.5</v>
       </c>
       <c r="K15">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -8794,13 +8806,13 @@
         <v>100</v>
       </c>
       <c r="T15" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U15" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="V15" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="W15">
         <v>0.1667</v>
@@ -8890,10 +8902,10 @@
         <v>91.2</v>
       </c>
       <c r="AZ15" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA15" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB15">
         <v>90.5</v>
@@ -8980,7 +8992,7 @@
         <v>1.182</v>
       </c>
       <c r="CD15" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE15">
         <v>1087</v>
@@ -9063,25 +9075,25 @@
         <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F16" t="s">
         <v>113</v>
       </c>
       <c r="G16" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H16" t="s">
         <v>199</v>
       </c>
       <c r="I16" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J16">
-        <v>160.2</v>
+        <v>166.5</v>
       </c>
       <c r="K16">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -9108,13 +9120,13 @@
         <v>75</v>
       </c>
       <c r="T16" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U16" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V16" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W16">
         <v>0.1667</v>
@@ -9204,10 +9216,10 @@
         <v>91.40000000000001</v>
       </c>
       <c r="AZ16" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA16" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB16">
         <v>88.5</v>
@@ -9294,7 +9306,7 @@
         <v>1.1862</v>
       </c>
       <c r="CD16" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE16">
         <v>956</v>
@@ -9377,25 +9389,25 @@
         <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F17" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G17" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="H17" t="s">
         <v>199</v>
       </c>
       <c r="I17" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="J17">
-        <v>160.2</v>
+        <v>166.5</v>
       </c>
       <c r="K17">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -9422,13 +9434,13 @@
         <v>75</v>
       </c>
       <c r="T17" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U17" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V17" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W17">
         <v>0.1667</v>
@@ -9518,10 +9530,10 @@
         <v>91.8</v>
       </c>
       <c r="AZ17" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA17" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB17">
         <v>86.2</v>
@@ -9608,7 +9620,7 @@
         <v>1.1921</v>
       </c>
       <c r="CD17" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE17">
         <v>770</v>
@@ -9691,25 +9703,25 @@
         <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F18" t="s">
         <v>111</v>
       </c>
       <c r="G18" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I18" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J18">
-        <v>293.4</v>
+        <v>299.7</v>
       </c>
       <c r="K18">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -9736,13 +9748,13 @@
         <v>100</v>
       </c>
       <c r="T18" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U18" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="V18" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="W18">
         <v>0.1667</v>
@@ -9832,10 +9844,10 @@
         <v>166.8</v>
       </c>
       <c r="AZ18" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="BA18" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="BB18">
         <v>93</v>
@@ -9922,7 +9934,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD18" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE18">
         <v>858</v>
@@ -10005,25 +10017,25 @@
         <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F19" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="G19" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H19" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I19" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J19">
-        <v>293.4</v>
+        <v>299.7</v>
       </c>
       <c r="K19">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -10050,13 +10062,13 @@
         <v>75</v>
       </c>
       <c r="T19" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U19" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="V19" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="W19">
         <v>0.1667</v>
@@ -10146,10 +10158,10 @@
         <v>176.1</v>
       </c>
       <c r="AZ19" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA19" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB19">
         <v>89.8</v>
@@ -10236,7 +10248,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD19" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE19">
         <v>858</v>
@@ -10287,7 +10299,7 @@
         <v>194</v>
       </c>
       <c r="CU19">
-        <v>25.3</v>
+        <v>25.2</v>
       </c>
       <c r="CV19" t="s">
         <v>195</v>
@@ -10319,25 +10331,25 @@
         <v>123</v>
       </c>
       <c r="E20" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F20" t="s">
         <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H20" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I20" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J20">
-        <v>293.4</v>
+        <v>299.7</v>
       </c>
       <c r="K20">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -10364,13 +10376,13 @@
         <v>18.8</v>
       </c>
       <c r="T20" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U20" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V20" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W20">
         <v>0.1667</v>
@@ -10397,7 +10409,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE20" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AF20">
         <v>85</v>
@@ -10460,10 +10472,10 @@
         <v>235.5</v>
       </c>
       <c r="AZ20" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA20" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB20">
         <v>54.6</v>
@@ -10550,7 +10562,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD20" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE20">
         <v>858</v>
@@ -10633,25 +10645,25 @@
         <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F21" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G21" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H21" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I21" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="J21">
-        <v>293.4</v>
+        <v>299.7</v>
       </c>
       <c r="K21">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -10678,13 +10690,13 @@
         <v>18.8</v>
       </c>
       <c r="T21" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U21" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V21" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W21">
         <v>0.1667</v>
@@ -10711,7 +10723,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE21" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AF21">
         <v>82.5</v>
@@ -10774,10 +10786,10 @@
         <v>262.6</v>
       </c>
       <c r="AZ21" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BA21" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BB21">
         <v>22.4</v>
@@ -10864,7 +10876,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD21" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE21">
         <v>858</v>
@@ -10947,25 +10959,25 @@
         <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F22" t="s">
         <v>112</v>
       </c>
       <c r="G22" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H22" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I22" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J22">
-        <v>286.8</v>
+        <v>293.2</v>
       </c>
       <c r="K22">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -10992,13 +11004,13 @@
         <v>56.2</v>
       </c>
       <c r="T22" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U22" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V22" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W22">
         <v>0.0833</v>
@@ -11088,10 +11100,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="AZ22" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA22" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB22">
         <v>89.3</v>
@@ -11178,7 +11190,7 @@
         <v>1.1664</v>
       </c>
       <c r="CD22" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE22">
         <v>1553</v>
@@ -11261,25 +11273,25 @@
         <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F23" t="s">
         <v>115</v>
       </c>
       <c r="G23" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H23" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I23" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J23">
-        <v>286.8</v>
+        <v>293.2</v>
       </c>
       <c r="K23">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -11306,13 +11318,13 @@
         <v>75</v>
       </c>
       <c r="T23" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U23" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V23" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W23">
         <v>0.0833</v>
@@ -11402,10 +11414,10 @@
         <v>85.5</v>
       </c>
       <c r="AZ23" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA23" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB23">
         <v>88.2</v>
@@ -11492,7 +11504,7 @@
         <v>1.1714</v>
       </c>
       <c r="CD23" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE23">
         <v>1404</v>
@@ -11575,25 +11587,25 @@
         <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F24" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G24" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I24" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J24">
-        <v>286.8</v>
+        <v>293.2</v>
       </c>
       <c r="K24">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -11620,13 +11632,13 @@
         <v>56.2</v>
       </c>
       <c r="T24" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U24" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V24" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W24">
         <v>0.0833</v>
@@ -11716,10 +11728,10 @@
         <v>86.90000000000001</v>
       </c>
       <c r="AZ24" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA24" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB24">
         <v>87.3</v>
@@ -11806,7 +11818,7 @@
         <v>1.1794</v>
       </c>
       <c r="CD24" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE24">
         <v>1152</v>
@@ -11889,25 +11901,25 @@
         <v>124</v>
       </c>
       <c r="E25" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F25" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G25" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="H25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I25" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J25">
-        <v>286.8</v>
+        <v>293.2</v>
       </c>
       <c r="K25">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -11934,13 +11946,13 @@
         <v>56.2</v>
       </c>
       <c r="T25" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U25" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V25" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W25">
         <v>0.0833</v>
@@ -12030,10 +12042,10 @@
         <v>90</v>
       </c>
       <c r="AZ25" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA25" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB25">
         <v>89.8</v>
@@ -12120,7 +12132,7 @@
         <v>1.1854</v>
       </c>
       <c r="CD25" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE25">
         <v>961</v>
@@ -12203,25 +12215,25 @@
         <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F26" t="s">
         <v>113</v>
       </c>
       <c r="G26" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I26" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J26">
-        <v>369.6</v>
+        <v>376</v>
       </c>
       <c r="K26">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -12248,13 +12260,13 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U26" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V26" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W26">
         <v>0.1667</v>
@@ -12344,10 +12356,10 @@
         <v>288.9</v>
       </c>
       <c r="AZ26" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="BA26" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="BB26">
         <v>97.7</v>
@@ -12434,7 +12446,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD26" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE26">
         <v>858</v>
@@ -12517,25 +12529,25 @@
         <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F27" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="G27" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H27" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I27" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J27">
-        <v>369.6</v>
+        <v>376</v>
       </c>
       <c r="K27">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -12562,13 +12574,13 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U27" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V27" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W27">
         <v>0.1667</v>
@@ -12595,7 +12607,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="AF27">
         <v>87.8</v>
@@ -12658,10 +12670,10 @@
         <v>297.8</v>
       </c>
       <c r="AZ27" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="BA27" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="BB27">
         <v>97.90000000000001</v>
@@ -12748,7 +12760,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD27" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE27">
         <v>858</v>
@@ -12831,25 +12843,25 @@
         <v>125</v>
       </c>
       <c r="E28" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G28" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H28" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I28" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J28">
-        <v>369.6</v>
+        <v>376</v>
       </c>
       <c r="K28">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -12876,13 +12888,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U28" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V28" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W28">
         <v>0.1667</v>
@@ -12909,7 +12921,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="AF28">
         <v>85.59999999999999</v>
@@ -12972,10 +12984,10 @@
         <v>299</v>
       </c>
       <c r="AZ28" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="BA28" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="BB28">
         <v>95</v>
@@ -13062,7 +13074,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD28" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE28">
         <v>858</v>
@@ -13145,25 +13157,25 @@
         <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F29" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="G29" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="H29" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="I29" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J29">
-        <v>369.6</v>
+        <v>376</v>
       </c>
       <c r="K29">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -13190,13 +13202,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U29" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V29" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W29">
         <v>0.1667</v>
@@ -13286,10 +13298,10 @@
         <v>300.2</v>
       </c>
       <c r="AZ29" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="BA29" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="BB29">
         <v>83.8</v>
@@ -13376,7 +13388,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD29" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE29">
         <v>858</v>
@@ -13459,25 +13471,25 @@
         <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F30" t="s">
         <v>114</v>
       </c>
       <c r="G30" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H30" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I30" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J30">
-        <v>144.2</v>
+        <v>150.5</v>
       </c>
       <c r="K30">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -13504,13 +13516,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U30" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V30" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W30">
         <v>0.6667</v>
@@ -13600,10 +13612,10 @@
         <v>269</v>
       </c>
       <c r="AZ30" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BA30" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BB30">
         <v>75.7</v>
@@ -13690,7 +13702,7 @@
         <v>1.1321</v>
       </c>
       <c r="CD30" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE30">
         <v>2463</v>
@@ -13773,25 +13785,25 @@
         <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F31" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="G31" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H31" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I31" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J31">
-        <v>144.2</v>
+        <v>150.5</v>
       </c>
       <c r="K31">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -13818,13 +13830,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U31" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V31" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W31">
         <v>0.6667</v>
@@ -13914,10 +13926,10 @@
         <v>260</v>
       </c>
       <c r="AZ31" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BA31" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BB31">
         <v>61.7</v>
@@ -14004,7 +14016,7 @@
         <v>1.1359</v>
       </c>
       <c r="CD31" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE31">
         <v>2353</v>
@@ -14087,25 +14099,25 @@
         <v>126</v>
       </c>
       <c r="E32" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F32" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G32" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H32" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I32" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J32">
-        <v>144.2</v>
+        <v>150.5</v>
       </c>
       <c r="K32">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -14132,13 +14144,13 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U32" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V32" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W32">
         <v>0.6667</v>
@@ -14228,10 +14240,10 @@
         <v>230.3</v>
       </c>
       <c r="AZ32" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BA32" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BB32">
         <v>50.5</v>
@@ -14318,7 +14330,7 @@
         <v>1.1434</v>
       </c>
       <c r="CD32" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE32">
         <v>2125</v>
@@ -14369,7 +14381,7 @@
         <v>193</v>
       </c>
       <c r="CU32">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="CV32" t="s">
         <v>193</v>
@@ -14401,25 +14413,25 @@
         <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F33" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="G33" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H33" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I33" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J33">
-        <v>144.2</v>
+        <v>150.5</v>
       </c>
       <c r="K33">
-        <v>24.5</v>
+        <v>24.4</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -14446,13 +14458,13 @@
         <v>56.2</v>
       </c>
       <c r="T33" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U33" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V33" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W33">
         <v>0.6667</v>
@@ -14542,10 +14554,10 @@
         <v>172.8</v>
       </c>
       <c r="AZ33" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BA33" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BB33">
         <v>20.2</v>
@@ -14632,7 +14644,7 @@
         <v>1.1491</v>
       </c>
       <c r="CD33" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE33">
         <v>1950</v>
@@ -14715,25 +14727,25 @@
         <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F34" t="s">
         <v>115</v>
       </c>
       <c r="G34" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I34" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J34">
-        <v>77.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K34">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -14760,13 +14772,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U34" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V34" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W34">
         <v>0.0833</v>
@@ -14856,10 +14868,10 @@
         <v>99.90000000000001</v>
       </c>
       <c r="AZ34" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA34" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB34">
         <v>97.40000000000001</v>
@@ -14946,7 +14958,7 @@
         <v>1.1682</v>
       </c>
       <c r="CD34" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE34">
         <v>1479</v>
@@ -15029,25 +15041,25 @@
         <v>127</v>
       </c>
       <c r="E35" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F35" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="G35" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H35" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I35" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J35">
-        <v>77.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K35">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -15074,13 +15086,13 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U35" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V35" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W35">
         <v>0.0833</v>
@@ -15164,16 +15176,16 @@
         <v>4.1</v>
       </c>
       <c r="AX35" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AY35">
         <v>103</v>
       </c>
       <c r="AZ35" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA35" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB35">
         <v>87.90000000000001</v>
@@ -15260,7 +15272,7 @@
         <v>1.1727</v>
       </c>
       <c r="CD35" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE35">
         <v>1331</v>
@@ -15343,25 +15355,25 @@
         <v>127</v>
       </c>
       <c r="E36" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F36" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G36" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H36" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I36" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J36">
-        <v>77.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K36">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="L36">
         <v>5</v>
@@ -15388,13 +15400,13 @@
         <v>56.2</v>
       </c>
       <c r="T36" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U36" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V36" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W36">
         <v>0.0833</v>
@@ -15484,10 +15496,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="AZ36" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA36" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB36">
         <v>77.09999999999999</v>
@@ -15574,7 +15586,7 @@
         <v>1.1776</v>
       </c>
       <c r="CD36" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE36">
         <v>1170</v>
@@ -15657,25 +15669,25 @@
         <v>127</v>
       </c>
       <c r="E37" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F37" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="G37" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="H37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I37" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="J37">
-        <v>77.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K37">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -15702,13 +15714,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U37" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="V37" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="W37">
         <v>0.0833</v>
@@ -15792,16 +15804,16 @@
         <v>7.7</v>
       </c>
       <c r="AX37" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AY37">
         <v>119.3</v>
       </c>
       <c r="AZ37" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA37" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB37">
         <v>73.8</v>
@@ -15888,7 +15900,7 @@
         <v>1.1808</v>
       </c>
       <c r="CD37" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE37">
         <v>1061</v>
@@ -15971,25 +15983,25 @@
         <v>128</v>
       </c>
       <c r="E38" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F38" t="s">
         <v>116</v>
       </c>
       <c r="G38" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H38" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I38" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J38">
-        <v>94.7</v>
+        <v>101</v>
       </c>
       <c r="K38">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -16016,13 +16028,13 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U38" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V38" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W38">
         <v>0.1667</v>
@@ -16112,10 +16124,10 @@
         <v>286.7</v>
       </c>
       <c r="AZ38" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="BA38" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="BB38">
         <v>88.7</v>
@@ -16202,7 +16214,7 @@
         <v>1.0981</v>
       </c>
       <c r="CD38" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="CE38">
         <v>3534</v>
@@ -16285,25 +16297,25 @@
         <v>128</v>
       </c>
       <c r="E39" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F39" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G39" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H39" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I39" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J39">
-        <v>94.7</v>
+        <v>101</v>
       </c>
       <c r="K39">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -16330,13 +16342,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U39" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V39" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W39">
         <v>0.1667</v>
@@ -16426,10 +16438,10 @@
         <v>269.4</v>
       </c>
       <c r="AZ39" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BA39" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="BB39">
         <v>66.8</v>
@@ -16516,7 +16528,7 @@
         <v>1.1001</v>
       </c>
       <c r="CD39" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE39">
         <v>3470</v>
@@ -16599,25 +16611,25 @@
         <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F40" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G40" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I40" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J40">
-        <v>94.7</v>
+        <v>101</v>
       </c>
       <c r="K40">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -16644,13 +16656,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U40" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V40" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W40">
         <v>0.1667</v>
@@ -16740,10 +16752,10 @@
         <v>251</v>
       </c>
       <c r="AZ40" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BA40" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BB40">
         <v>66</v>
@@ -16830,7 +16842,7 @@
         <v>1.1037</v>
       </c>
       <c r="CD40" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE40">
         <v>3343</v>
@@ -16913,25 +16925,25 @@
         <v>128</v>
       </c>
       <c r="E41" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F41" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G41" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="H41" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I41" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J41">
-        <v>94.7</v>
+        <v>101</v>
       </c>
       <c r="K41">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="L41">
         <v>5</v>
@@ -16958,13 +16970,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U41" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V41" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W41">
         <v>0.1667</v>
@@ -17054,10 +17066,10 @@
         <v>232.4</v>
       </c>
       <c r="AZ41" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BA41" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BB41">
         <v>63.4</v>
@@ -17144,7 +17156,7 @@
         <v>1.1126</v>
       </c>
       <c r="CD41" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE41">
         <v>3045</v>
@@ -17227,25 +17239,25 @@
         <v>129</v>
       </c>
       <c r="E42" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F42" t="s">
         <v>116</v>
       </c>
       <c r="G42" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H42" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I42" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J42">
-        <v>324.7</v>
+        <v>331</v>
       </c>
       <c r="K42">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="L42">
         <v>5</v>
@@ -17272,13 +17284,13 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U42" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V42" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W42">
         <v>0.1667</v>
@@ -17368,10 +17380,10 @@
         <v>229.8</v>
       </c>
       <c r="AZ42" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA42" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB42">
         <v>96.59999999999999</v>
@@ -17458,7 +17470,7 @@
         <v>1.1402</v>
       </c>
       <c r="CD42" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE42">
         <v>2185</v>
@@ -17541,25 +17553,25 @@
         <v>129</v>
       </c>
       <c r="E43" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F43" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G43" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H43" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I43" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J43">
-        <v>324.7</v>
+        <v>331</v>
       </c>
       <c r="K43">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -17586,13 +17598,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U43" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V43" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W43">
         <v>0.1667</v>
@@ -17682,10 +17694,10 @@
         <v>227.8</v>
       </c>
       <c r="AZ43" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA43" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB43">
         <v>95.40000000000001</v>
@@ -17772,7 +17784,7 @@
         <v>1.1411</v>
       </c>
       <c r="CD43" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE43">
         <v>2151</v>
@@ -17855,25 +17867,25 @@
         <v>129</v>
       </c>
       <c r="E44" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F44" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G44" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H44" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I44" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J44">
-        <v>324.7</v>
+        <v>331</v>
       </c>
       <c r="K44">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="L44">
         <v>5</v>
@@ -17900,13 +17912,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U44" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V44" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W44">
         <v>0.1667</v>
@@ -17996,10 +18008,10 @@
         <v>219.2</v>
       </c>
       <c r="AZ44" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA44" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB44">
         <v>92.59999999999999</v>
@@ -18086,7 +18098,7 @@
         <v>1.1444</v>
       </c>
       <c r="CD44" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE44">
         <v>2048</v>
@@ -18169,25 +18181,25 @@
         <v>129</v>
       </c>
       <c r="E45" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F45" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G45" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="H45" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I45" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="J45">
-        <v>324.7</v>
+        <v>331</v>
       </c>
       <c r="K45">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -18214,13 +18226,13 @@
         <v>56.2</v>
       </c>
       <c r="T45" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U45" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V45" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W45">
         <v>0.1667</v>
@@ -18310,10 +18322,10 @@
         <v>198.6</v>
       </c>
       <c r="AZ45" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA45" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB45">
         <v>83.3</v>
@@ -18400,7 +18412,7 @@
         <v>1.1441</v>
       </c>
       <c r="CD45" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE45">
         <v>2050</v>
@@ -18483,25 +18495,25 @@
         <v>130</v>
       </c>
       <c r="E46" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F46" t="s">
         <v>116</v>
       </c>
       <c r="G46" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H46" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I46" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J46">
-        <v>89.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="K46">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="L46">
         <v>5</v>
@@ -18528,13 +18540,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U46" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V46" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W46">
         <v>0.1667</v>
@@ -18624,10 +18636,10 @@
         <v>235.1</v>
       </c>
       <c r="AZ46" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA46" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB46">
         <v>89.8</v>
@@ -18714,7 +18726,7 @@
         <v>1.1299</v>
       </c>
       <c r="CD46" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE46">
         <v>2507</v>
@@ -18797,25 +18809,25 @@
         <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F47" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G47" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H47" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I47" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J47">
-        <v>89.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="K47">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="L47">
         <v>5</v>
@@ -18842,13 +18854,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U47" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V47" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W47">
         <v>0.1667</v>
@@ -18938,10 +18950,10 @@
         <v>235.1</v>
       </c>
       <c r="AZ47" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA47" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB47">
         <v>93.90000000000001</v>
@@ -19028,7 +19040,7 @@
         <v>1.1306</v>
       </c>
       <c r="CD47" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE47">
         <v>2485</v>
@@ -19111,25 +19123,25 @@
         <v>130</v>
       </c>
       <c r="E48" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F48" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="G48" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H48" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I48" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J48">
-        <v>89.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="K48">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="L48">
         <v>5</v>
@@ -19156,13 +19168,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U48" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V48" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W48">
         <v>0.1667</v>
@@ -19252,10 +19264,10 @@
         <v>219.9</v>
       </c>
       <c r="AZ48" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA48" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB48">
         <v>89.5</v>
@@ -19342,7 +19354,7 @@
         <v>1.1344</v>
       </c>
       <c r="CD48" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE48">
         <v>2366</v>
@@ -19425,25 +19437,25 @@
         <v>130</v>
       </c>
       <c r="E49" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F49" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="G49" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="H49" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I49" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J49">
-        <v>89.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="K49">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="L49">
         <v>5</v>
@@ -19470,13 +19482,13 @@
         <v>56.2</v>
       </c>
       <c r="T49" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U49" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V49" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W49">
         <v>0.1667</v>
@@ -19566,10 +19578,10 @@
         <v>206.6</v>
       </c>
       <c r="AZ49" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA49" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB49">
         <v>86.8</v>
@@ -19656,7 +19668,7 @@
         <v>1.1405</v>
       </c>
       <c r="CD49" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE49">
         <v>2170</v>
@@ -19739,25 +19751,25 @@
         <v>131</v>
       </c>
       <c r="E50" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F50" t="s">
         <v>117</v>
       </c>
       <c r="G50" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H50" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I50" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J50">
-        <v>381</v>
+        <v>387.3</v>
       </c>
       <c r="K50">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="L50">
         <v>5</v>
@@ -19784,13 +19796,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U50" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V50" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W50">
         <v>0.25</v>
@@ -19880,10 +19892,10 @@
         <v>123.8</v>
       </c>
       <c r="AZ50" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA50" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB50">
         <v>90.5</v>
@@ -19970,7 +19982,7 @@
         <v>1.1795</v>
       </c>
       <c r="CD50" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE50">
         <v>1157</v>
@@ -20053,25 +20065,25 @@
         <v>131</v>
       </c>
       <c r="E51" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F51" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="G51" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H51" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I51" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J51">
-        <v>381</v>
+        <v>387.3</v>
       </c>
       <c r="K51">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="L51">
         <v>5</v>
@@ -20098,13 +20110,13 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U51" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V51" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W51">
         <v>0.25</v>
@@ -20194,10 +20206,10 @@
         <v>125</v>
       </c>
       <c r="AZ51" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BA51" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="BB51">
         <v>90.90000000000001</v>
@@ -20284,7 +20296,7 @@
         <v>1.1876</v>
       </c>
       <c r="CD51" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE51">
         <v>907</v>
@@ -20367,25 +20379,25 @@
         <v>131</v>
       </c>
       <c r="E52" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F52" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G52" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H52" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I52" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J52">
-        <v>381</v>
+        <v>387.3</v>
       </c>
       <c r="K52">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="L52">
         <v>5</v>
@@ -20412,13 +20424,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U52" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V52" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W52">
         <v>0.25</v>
@@ -20502,16 +20514,16 @@
         <v>7.7</v>
       </c>
       <c r="AX52" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AY52">
         <v>123.6</v>
       </c>
       <c r="AZ52" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA52" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB52">
         <v>90.90000000000001</v>
@@ -20598,7 +20610,7 @@
         <v>1.1936</v>
       </c>
       <c r="CD52" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE52">
         <v>726</v>
@@ -20681,25 +20693,25 @@
         <v>131</v>
       </c>
       <c r="E53" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F53" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="G53" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="H53" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I53" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J53">
-        <v>381</v>
+        <v>387.3</v>
       </c>
       <c r="K53">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -20726,13 +20738,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U53" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="V53" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="W53">
         <v>0.25</v>
@@ -20816,16 +20828,16 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AX53" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AY53">
         <v>121.1</v>
       </c>
       <c r="AZ53" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA53" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB53">
         <v>73.2</v>
@@ -20912,7 +20924,7 @@
         <v>1.1969</v>
       </c>
       <c r="CD53" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE53">
         <v>624</v>
@@ -20963,7 +20975,7 @@
         <v>193</v>
       </c>
       <c r="CU53">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="CV53" t="s">
         <v>193</v>
@@ -20995,25 +21007,25 @@
         <v>132</v>
       </c>
       <c r="E54" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F54" t="s">
         <v>118</v>
       </c>
       <c r="G54" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H54" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I54" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J54">
-        <v>29.8</v>
+        <v>36.2</v>
       </c>
       <c r="K54">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="L54">
         <v>5</v>
@@ -21040,13 +21052,13 @@
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U54" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V54" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W54">
         <v>0.25</v>
@@ -21136,10 +21148,10 @@
         <v>212</v>
       </c>
       <c r="AZ54" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BA54" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BB54">
         <v>33.1</v>
@@ -21226,7 +21238,7 @@
         <v>1.1284</v>
       </c>
       <c r="CD54" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE54">
         <v>2482</v>
@@ -21277,7 +21289,7 @@
         <v>193</v>
       </c>
       <c r="CU54">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="CV54" t="s">
         <v>193</v>
@@ -21309,25 +21321,25 @@
         <v>132</v>
       </c>
       <c r="E55" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F55" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G55" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H55" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I55" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J55">
-        <v>29.8</v>
+        <v>36.2</v>
       </c>
       <c r="K55">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="L55">
         <v>5</v>
@@ -21354,13 +21366,13 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U55" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V55" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W55">
         <v>0.25</v>
@@ -21387,7 +21399,7 @@
         <v>0.3</v>
       </c>
       <c r="AE55" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="AF55">
         <v>87.7</v>
@@ -21450,10 +21462,10 @@
         <v>148.5</v>
       </c>
       <c r="AZ55" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BA55" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BB55">
         <v>30.6</v>
@@ -21540,7 +21552,7 @@
         <v>1.1302</v>
       </c>
       <c r="CD55" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE55">
         <v>2429</v>
@@ -21623,25 +21635,25 @@
         <v>132</v>
       </c>
       <c r="E56" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F56" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G56" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H56" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I56" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J56">
-        <v>29.8</v>
+        <v>36.2</v>
       </c>
       <c r="K56">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="L56">
         <v>5</v>
@@ -21668,13 +21680,13 @@
         <v>56.2</v>
       </c>
       <c r="T56" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U56" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V56" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W56">
         <v>0.25</v>
@@ -21758,16 +21770,16 @@
         <v>4.2</v>
       </c>
       <c r="AX56" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="AY56">
         <v>103.1</v>
       </c>
       <c r="AZ56" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BA56" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="BB56">
         <v>27.1</v>
@@ -21854,7 +21866,7 @@
         <v>1.1345</v>
       </c>
       <c r="CD56" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE56">
         <v>2284</v>
@@ -21937,25 +21949,25 @@
         <v>132</v>
       </c>
       <c r="E57" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F57" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G57" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H57" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="I57" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J57">
-        <v>29.8</v>
+        <v>36.2</v>
       </c>
       <c r="K57">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="L57">
         <v>5</v>
@@ -21982,13 +21994,13 @@
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U57" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V57" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W57">
         <v>0.25</v>
@@ -22078,10 +22090,10 @@
         <v>142.5</v>
       </c>
       <c r="AZ57" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BA57" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="BB57">
         <v>68.5</v>
@@ -22168,7 +22180,7 @@
         <v>1.1434</v>
       </c>
       <c r="CD57" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="CE57">
         <v>2004</v>
@@ -22251,25 +22263,25 @@
         <v>133</v>
       </c>
       <c r="E58" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="F58" t="s">
         <v>118</v>
       </c>
       <c r="G58" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H58" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I58" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J58">
-        <v>119.1</v>
+        <v>125.4</v>
       </c>
       <c r="K58">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="L58">
         <v>5</v>
@@ -22296,13 +22308,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U58" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="V58" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="W58">
         <v>0.25</v>
@@ -22392,10 +22404,10 @@
         <v>181</v>
       </c>
       <c r="AZ58" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BA58" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BB58">
         <v>92.90000000000001</v>
@@ -22482,7 +22494,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD58" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE58">
         <v>858</v>
@@ -22565,25 +22577,25 @@
         <v>133</v>
       </c>
       <c r="E59" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F59" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="G59" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H59" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I59" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J59">
-        <v>119.1</v>
+        <v>125.4</v>
       </c>
       <c r="K59">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -22610,13 +22622,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U59" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="V59" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="W59">
         <v>0.25</v>
@@ -22706,10 +22718,10 @@
         <v>178.8</v>
       </c>
       <c r="AZ59" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BA59" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BB59">
         <v>93.09999999999999</v>
@@ -22796,7 +22808,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD59" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE59">
         <v>858</v>
@@ -22879,25 +22891,25 @@
         <v>133</v>
       </c>
       <c r="E60" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F60" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="G60" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H60" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I60" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J60">
-        <v>119.1</v>
+        <v>125.4</v>
       </c>
       <c r="K60">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -22924,13 +22936,13 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U60" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V60" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W60">
         <v>0.25</v>
@@ -23020,10 +23032,10 @@
         <v>177.8</v>
       </c>
       <c r="AZ60" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BA60" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BB60">
         <v>95.3</v>
@@ -23110,7 +23122,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD60" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE60">
         <v>858</v>
@@ -23193,25 +23205,25 @@
         <v>133</v>
       </c>
       <c r="E61" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F61" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G61" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H61" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="I61" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="J61">
-        <v>119.1</v>
+        <v>125.4</v>
       </c>
       <c r="K61">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="L61">
         <v>5</v>
@@ -23238,13 +23250,13 @@
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="U61" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="V61" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="W61">
         <v>0.25</v>
@@ -23334,10 +23346,10 @@
         <v>176.9</v>
       </c>
       <c r="AZ61" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BA61" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="BB61">
         <v>95.40000000000001</v>
@@ -23424,7 +23436,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD61" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="CE61">
         <v>858</v>

--- a/mlb_weather_professional_v5_2026_07_25.xlsx
+++ b/mlb_weather_professional_v5_2026_07_25.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2028" uniqueCount="392">
   <si>
     <t>Date</t>
   </si>
@@ -611,49 +611,46 @@
     <t>MEDIUM</t>
   </si>
   <si>
-    <t>2026-07-24 06:17:13 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:14 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:15 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:16 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:17 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:19 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:20 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:22 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:23 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:24 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:25 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:26 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:27 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:29 PM PDT</t>
-  </si>
-  <si>
-    <t>2026-07-24 06:17:30 PM PDT</t>
+    <t>2026-07-24 06:24:29 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:30 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:31 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:32 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:33 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:34 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:35 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:36 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:37 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:38 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:39 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:40 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:41 PM PDT</t>
+  </si>
+  <si>
+    <t>2026-07-24 06:24:42 PM PDT</t>
   </si>
   <si>
     <t>Period</t>
@@ -1028,49 +1025,46 @@
     <t>09:15 PM CDT</t>
   </si>
   <si>
-    <t>2026-07-25 01:17:13 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:14 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:15 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:16 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:17 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:19 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:20 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:22 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:23 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:24 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:25 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:26 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:27 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:29 UTC</t>
-  </si>
-  <si>
-    <t>2026-07-25 01:17:30 UTC</t>
+    <t>2026-07-25 01:24:29 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:30 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:31 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:32 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:33 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:34 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:35 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:36 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:37 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:38 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:39 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:40 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:41 UTC</t>
+  </si>
+  <si>
+    <t>2026-07-25 01:24:42 UTC</t>
   </si>
   <si>
     <t>2026-07-24T20:24:19+00:00</t>
@@ -2012,7 +2006,7 @@
         <v>196</v>
       </c>
       <c r="AZ2">
-        <v>292.9</v>
+        <v>300.2</v>
       </c>
       <c r="BA2">
         <v>5</v>
@@ -2152,7 +2146,7 @@
         <v>0</v>
       </c>
       <c r="AT3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU3" t="s">
         <v>193</v>
@@ -2164,13 +2158,13 @@
         <v>193</v>
       </c>
       <c r="AX3">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="AY3" t="s">
         <v>197</v>
       </c>
       <c r="AZ3">
-        <v>83.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="BA3">
         <v>5</v>
@@ -2328,7 +2322,7 @@
         <v>198</v>
       </c>
       <c r="AZ4">
-        <v>291.3</v>
+        <v>298.5</v>
       </c>
       <c r="BA4">
         <v>5</v>
@@ -2486,7 +2480,7 @@
         <v>199</v>
       </c>
       <c r="AZ5">
-        <v>166.5</v>
+        <v>173.8</v>
       </c>
       <c r="BA5">
         <v>5</v>
@@ -2644,7 +2638,7 @@
         <v>200</v>
       </c>
       <c r="AZ6">
-        <v>299.7</v>
+        <v>307</v>
       </c>
       <c r="BA6">
         <v>5</v>
@@ -2784,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="AT7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="s">
         <v>193</v>
@@ -2802,7 +2796,7 @@
         <v>201</v>
       </c>
       <c r="AZ7">
-        <v>293.2</v>
+        <v>300.4</v>
       </c>
       <c r="BA7">
         <v>5</v>
@@ -2960,7 +2954,7 @@
         <v>202</v>
       </c>
       <c r="AZ8">
-        <v>376</v>
+        <v>383.2</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -3100,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="AT9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="s">
         <v>193</v>
@@ -3112,13 +3106,13 @@
         <v>193</v>
       </c>
       <c r="AX9">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AY9" t="s">
         <v>203</v>
       </c>
       <c r="AZ9">
-        <v>150.5</v>
+        <v>157.7</v>
       </c>
       <c r="BA9">
         <v>5</v>
@@ -3276,7 +3270,7 @@
         <v>204</v>
       </c>
       <c r="AZ10">
-        <v>84.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="BA10">
         <v>5</v>
@@ -3428,13 +3422,13 @@
         <v>193</v>
       </c>
       <c r="AX11">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="AY11" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AZ11">
-        <v>101</v>
+        <v>108.3</v>
       </c>
       <c r="BA11">
         <v>5</v>
@@ -3589,10 +3583,10 @@
         <v>14.1</v>
       </c>
       <c r="AY12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AZ12">
-        <v>331</v>
+        <v>338.2</v>
       </c>
       <c r="BA12">
         <v>5</v>
@@ -3747,10 +3741,10 @@
         <v>7.5</v>
       </c>
       <c r="AY13" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AZ13">
-        <v>95.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="BA13">
         <v>5</v>
@@ -3905,10 +3899,10 @@
         <v>12.3</v>
       </c>
       <c r="AY14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AZ14">
-        <v>387.3</v>
+        <v>394.5</v>
       </c>
       <c r="BA14">
         <v>5</v>
@@ -4063,10 +4057,10 @@
         <v>11.8</v>
       </c>
       <c r="AY15" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AZ15">
-        <v>36.2</v>
+        <v>43.4</v>
       </c>
       <c r="BA15">
         <v>5</v>
@@ -4221,10 +4215,10 @@
         <v>9.4</v>
       </c>
       <c r="AY16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AZ16">
-        <v>125.4</v>
+        <v>132.6</v>
       </c>
       <c r="BA16">
         <v>5</v>
@@ -4365,286 +4359,286 @@
         <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>212</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>213</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>50</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>52</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>223</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="AJ1" s="1" t="s">
+      <c r="AK1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="AP1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="AV1" s="1" t="s">
+      <c r="AW1" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="AW1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="AY1" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="BC1" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="BC1" s="1" t="s">
+      <c r="BD1" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="BD1" s="1" t="s">
+      <c r="BE1" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="BF1" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="BF1" s="1" t="s">
+      <c r="BG1" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="BG1" s="1" t="s">
+      <c r="BH1" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="BH1" s="1" t="s">
+      <c r="BI1" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="BJ1" s="1" t="s">
+      <c r="BK1" s="1" t="s">
         <v>265</v>
       </c>
-      <c r="BK1" s="1" t="s">
+      <c r="BL1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="BL1" s="1" t="s">
+      <c r="BM1" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="BM1" s="1" t="s">
+      <c r="BN1" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="BN1" s="1" t="s">
+      <c r="BO1" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="BO1" s="1" t="s">
+      <c r="BP1" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BQ1" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BR1" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="BR1" s="1" t="s">
+      <c r="BS1" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="BS1" s="1" t="s">
+      <c r="BT1" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="BT1" s="1" t="s">
+      <c r="BU1" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="BU1" s="1" t="s">
+      <c r="BV1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="BV1" s="1" t="s">
+      <c r="BW1" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="BW1" s="1" t="s">
+      <c r="BX1" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="BX1" s="1" t="s">
+      <c r="BY1" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="BY1" s="1" t="s">
+      <c r="BZ1" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="BZ1" s="1" t="s">
+      <c r="CA1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="CA1" s="1" t="s">
+      <c r="CB1" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="CB1" s="1" t="s">
+      <c r="CC1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="CC1" s="1" t="s">
+      <c r="CD1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="CD1" s="1" t="s">
+      <c r="CE1" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="CE1" s="1" t="s">
+      <c r="CF1" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="CF1" s="1" t="s">
+      <c r="CG1" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="CG1" s="1" t="s">
+      <c r="CH1" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="CH1" s="1" t="s">
+      <c r="CI1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="CI1" s="1" t="s">
+      <c r="CJ1" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="CJ1" s="1" t="s">
+      <c r="CK1" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="CK1" s="1" t="s">
+      <c r="CL1" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="CL1" s="1" t="s">
+      <c r="CM1" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="CM1" s="1" t="s">
+      <c r="CN1" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="CN1" s="1" t="s">
+      <c r="CO1" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="CO1" s="1" t="s">
+      <c r="CP1" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="CP1" s="1" t="s">
+      <c r="CQ1" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="CQ1" s="1" t="s">
+      <c r="CR1" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="CR1" s="1" t="s">
+      <c r="CS1" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="CS1" s="1" t="s">
+      <c r="CT1" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="CT1" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="CU1" s="1" t="s">
         <v>49</v>
@@ -4653,16 +4647,16 @@
         <v>48</v>
       </c>
       <c r="CW1" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="CX1" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="CX1" s="1" t="s">
+      <c r="CY1" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="CY1" s="1" t="s">
+      <c r="CZ1" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="CZ1" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:104">
@@ -4679,25 +4673,25 @@
         <v>119</v>
       </c>
       <c r="E2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F2" t="s">
         <v>108</v>
       </c>
       <c r="G2" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H2" t="s">
         <v>196</v>
       </c>
       <c r="I2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J2">
-        <v>292.9</v>
+        <v>300.2</v>
       </c>
       <c r="K2">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="L2">
         <v>5</v>
@@ -4724,13 +4718,13 @@
         <v>0</v>
       </c>
       <c r="T2" t="s">
+        <v>362</v>
+      </c>
+      <c r="U2" t="s">
+        <v>363</v>
+      </c>
+      <c r="V2" t="s">
         <v>364</v>
-      </c>
-      <c r="U2" t="s">
-        <v>365</v>
-      </c>
-      <c r="V2" t="s">
-        <v>366</v>
       </c>
       <c r="W2">
         <v>0.1667</v>
@@ -4820,10 +4814,10 @@
         <v>237</v>
       </c>
       <c r="AZ2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB2">
         <v>96</v>
@@ -4910,7 +4904,7 @@
         <v>1.1468</v>
       </c>
       <c r="CD2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE2">
         <v>2100</v>
@@ -4961,7 +4955,7 @@
         <v>193</v>
       </c>
       <c r="CU2">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="CV2" t="s">
         <v>193</v>
@@ -4993,25 +4987,25 @@
         <v>119</v>
       </c>
       <c r="E3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H3" t="s">
         <v>196</v>
       </c>
       <c r="I3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J3">
-        <v>292.9</v>
+        <v>300.2</v>
       </c>
       <c r="K3">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="L3">
         <v>5</v>
@@ -5038,13 +5032,13 @@
         <v>100</v>
       </c>
       <c r="T3" t="s">
+        <v>362</v>
+      </c>
+      <c r="U3" t="s">
         <v>364</v>
       </c>
-      <c r="U3" t="s">
-        <v>366</v>
-      </c>
       <c r="V3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="W3">
         <v>0.1667</v>
@@ -5134,10 +5128,10 @@
         <v>215.3</v>
       </c>
       <c r="AZ3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA3" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB3">
         <v>93.3</v>
@@ -5224,7 +5218,7 @@
         <v>1.1421</v>
       </c>
       <c r="CD3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE3">
         <v>2250</v>
@@ -5275,7 +5269,7 @@
         <v>193</v>
       </c>
       <c r="CU3">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="CV3" t="s">
         <v>193</v>
@@ -5307,25 +5301,25 @@
         <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H4" t="s">
         <v>196</v>
       </c>
       <c r="I4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J4">
-        <v>292.9</v>
+        <v>300.2</v>
       </c>
       <c r="K4">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="L4">
         <v>5</v>
@@ -5352,13 +5346,13 @@
         <v>81.2</v>
       </c>
       <c r="T4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U4" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="V4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="W4">
         <v>0.1667</v>
@@ -5448,10 +5442,10 @@
         <v>210.5</v>
       </c>
       <c r="AZ4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB4">
         <v>91.59999999999999</v>
@@ -5538,7 +5532,7 @@
         <v>1.1398</v>
       </c>
       <c r="CD4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE4">
         <v>2320</v>
@@ -5621,25 +5615,25 @@
         <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F5" t="s">
         <v>111</v>
       </c>
       <c r="G5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H5" t="s">
         <v>196</v>
       </c>
       <c r="I5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="J5">
-        <v>292.9</v>
+        <v>300.2</v>
       </c>
       <c r="K5">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="L5">
         <v>5</v>
@@ -5666,13 +5660,13 @@
         <v>100</v>
       </c>
       <c r="T5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="V5" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="W5">
         <v>0.1667</v>
@@ -5762,10 +5756,10 @@
         <v>206.2</v>
       </c>
       <c r="AZ5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA5" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB5">
         <v>89.7</v>
@@ -5852,7 +5846,7 @@
         <v>1.138</v>
       </c>
       <c r="CD5" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE5">
         <v>2369</v>
@@ -5935,25 +5929,25 @@
         <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F6" t="s">
         <v>109</v>
       </c>
       <c r="G6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H6" t="s">
         <v>197</v>
       </c>
       <c r="I6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J6">
-        <v>83.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="K6">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="L6">
         <v>5</v>
@@ -5980,13 +5974,13 @@
         <v>81.2</v>
       </c>
       <c r="T6" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U6" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="V6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="W6">
         <v>0.0833</v>
@@ -6076,10 +6070,10 @@
         <v>91.5</v>
       </c>
       <c r="AZ6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB6">
         <v>90</v>
@@ -6166,7 +6160,7 @@
         <v>1.1581</v>
       </c>
       <c r="CD6" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE6">
         <v>1752</v>
@@ -6217,7 +6211,7 @@
         <v>193</v>
       </c>
       <c r="CU6">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CV6" t="s">
         <v>193</v>
@@ -6249,25 +6243,25 @@
         <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F7" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H7" t="s">
         <v>197</v>
       </c>
       <c r="I7" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J7">
-        <v>83.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="K7">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="L7">
         <v>5</v>
@@ -6294,13 +6288,13 @@
         <v>81.2</v>
       </c>
       <c r="T7" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U7" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="V7" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W7">
         <v>0.0833</v>
@@ -6390,10 +6384,10 @@
         <v>91.09999999999999</v>
       </c>
       <c r="AZ7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA7" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB7">
         <v>84.90000000000001</v>
@@ -6480,7 +6474,7 @@
         <v>1.1575</v>
       </c>
       <c r="CD7" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE7">
         <v>1774</v>
@@ -6531,7 +6525,7 @@
         <v>193</v>
       </c>
       <c r="CU7">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="CV7" t="s">
         <v>193</v>
@@ -6563,25 +6557,25 @@
         <v>120</v>
       </c>
       <c r="E8" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F8" t="s">
         <v>112</v>
       </c>
       <c r="G8" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H8" t="s">
         <v>197</v>
       </c>
       <c r="I8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J8">
-        <v>83.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="K8">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -6608,13 +6602,13 @@
         <v>81.2</v>
       </c>
       <c r="T8" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U8" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V8" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W8">
         <v>0.0833</v>
@@ -6704,10 +6698,10 @@
         <v>93.7</v>
       </c>
       <c r="AZ8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA8" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB8">
         <v>90.5</v>
@@ -6794,7 +6788,7 @@
         <v>1.1591</v>
       </c>
       <c r="CD8" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE8">
         <v>1723</v>
@@ -6877,25 +6871,25 @@
         <v>120</v>
       </c>
       <c r="E9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F9" t="s">
         <v>115</v>
       </c>
       <c r="G9" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H9" t="s">
         <v>197</v>
       </c>
       <c r="I9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J9">
-        <v>83.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="K9">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L9">
         <v>5</v>
@@ -6922,13 +6916,13 @@
         <v>56.2</v>
       </c>
       <c r="T9" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U9" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V9" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W9">
         <v>0.0833</v>
@@ -7018,10 +7012,10 @@
         <v>96.59999999999999</v>
       </c>
       <c r="AZ9" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA9" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB9">
         <v>92.3</v>
@@ -7108,7 +7102,7 @@
         <v>1.1631</v>
       </c>
       <c r="CD9" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE9">
         <v>1594</v>
@@ -7191,25 +7185,25 @@
         <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F10" t="s">
         <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H10" t="s">
         <v>198</v>
       </c>
       <c r="I10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J10">
-        <v>291.3</v>
+        <v>298.5</v>
       </c>
       <c r="K10">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -7236,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="T10" t="s">
+        <v>362</v>
+      </c>
+      <c r="U10" t="s">
+        <v>363</v>
+      </c>
+      <c r="V10" t="s">
         <v>364</v>
-      </c>
-      <c r="U10" t="s">
-        <v>365</v>
-      </c>
-      <c r="V10" t="s">
-        <v>366</v>
       </c>
       <c r="W10">
         <v>0.0833</v>
@@ -7332,10 +7326,10 @@
         <v>275.2</v>
       </c>
       <c r="AZ10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BA10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BB10">
         <v>86.09999999999999</v>
@@ -7422,7 +7416,7 @@
         <v>1.2186</v>
       </c>
       <c r="CD10" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE10">
         <v>-8</v>
@@ -7505,25 +7499,25 @@
         <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F11" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G11" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H11" t="s">
         <v>198</v>
       </c>
       <c r="I11" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J11">
-        <v>291.3</v>
+        <v>298.5</v>
       </c>
       <c r="K11">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="L11">
         <v>5</v>
@@ -7550,13 +7544,13 @@
         <v>0</v>
       </c>
       <c r="T11" t="s">
+        <v>362</v>
+      </c>
+      <c r="U11" t="s">
         <v>364</v>
       </c>
-      <c r="U11" t="s">
-        <v>366</v>
-      </c>
       <c r="V11" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="W11">
         <v>0.0833</v>
@@ -7646,10 +7640,10 @@
         <v>274.8</v>
       </c>
       <c r="AZ11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BA11" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BB11">
         <v>85.3</v>
@@ -7736,7 +7730,7 @@
         <v>1.2185</v>
       </c>
       <c r="CD11" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE11">
         <v>-4</v>
@@ -7819,25 +7813,25 @@
         <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H12" t="s">
         <v>198</v>
       </c>
       <c r="I12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J12">
-        <v>291.3</v>
+        <v>298.5</v>
       </c>
       <c r="K12">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L12">
         <v>5</v>
@@ -7864,13 +7858,13 @@
         <v>0</v>
       </c>
       <c r="T12" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U12" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="V12" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="W12">
         <v>0.0833</v>
@@ -7960,10 +7954,10 @@
         <v>274.8</v>
       </c>
       <c r="AZ12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BA12" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BB12">
         <v>85.7</v>
@@ -8050,7 +8044,7 @@
         <v>1.217</v>
       </c>
       <c r="CD12" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE12">
         <v>38</v>
@@ -8133,25 +8127,25 @@
         <v>121</v>
       </c>
       <c r="E13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G13" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H13" t="s">
         <v>198</v>
       </c>
       <c r="I13" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="J13">
-        <v>291.3</v>
+        <v>298.5</v>
       </c>
       <c r="K13">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L13">
         <v>5</v>
@@ -8178,13 +8172,13 @@
         <v>0</v>
       </c>
       <c r="T13" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U13" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="V13" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="W13">
         <v>0.0833</v>
@@ -8274,10 +8268,10 @@
         <v>274.6</v>
       </c>
       <c r="AZ13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BA13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BB13">
         <v>85.3</v>
@@ -8364,7 +8358,7 @@
         <v>1.2175</v>
       </c>
       <c r="CD13" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE13">
         <v>22</v>
@@ -8415,7 +8409,7 @@
         <v>193</v>
       </c>
       <c r="CU13">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="CV13" t="s">
         <v>193</v>
@@ -8447,25 +8441,25 @@
         <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F14" t="s">
         <v>111</v>
       </c>
       <c r="G14" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H14" t="s">
         <v>199</v>
       </c>
       <c r="I14" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J14">
-        <v>166.5</v>
+        <v>173.8</v>
       </c>
       <c r="K14">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="L14">
         <v>5</v>
@@ -8492,13 +8486,13 @@
         <v>100</v>
       </c>
       <c r="T14" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U14" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="V14" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="W14">
         <v>0.1667</v>
@@ -8588,10 +8582,10 @@
         <v>90.8</v>
       </c>
       <c r="AZ14" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA14" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB14">
         <v>91.5</v>
@@ -8678,7 +8672,7 @@
         <v>1.1798</v>
       </c>
       <c r="CD14" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE14">
         <v>1156</v>
@@ -8761,25 +8755,25 @@
         <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F15" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G15" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H15" t="s">
         <v>199</v>
       </c>
       <c r="I15" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J15">
-        <v>166.5</v>
+        <v>173.8</v>
       </c>
       <c r="K15">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="L15">
         <v>5</v>
@@ -8806,13 +8800,13 @@
         <v>100</v>
       </c>
       <c r="T15" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U15" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="V15" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W15">
         <v>0.1667</v>
@@ -8821,7 +8815,7 @@
         <v>4</v>
       </c>
       <c r="Y15">
-        <v>94.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="Z15">
         <v>42</v>
@@ -8902,10 +8896,10 @@
         <v>91.2</v>
       </c>
       <c r="AZ15" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA15" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB15">
         <v>90.5</v>
@@ -8992,7 +8986,7 @@
         <v>1.182</v>
       </c>
       <c r="CD15" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE15">
         <v>1087</v>
@@ -9075,25 +9069,25 @@
         <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F16" t="s">
         <v>113</v>
       </c>
       <c r="G16" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H16" t="s">
         <v>199</v>
       </c>
       <c r="I16" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J16">
-        <v>166.5</v>
+        <v>173.8</v>
       </c>
       <c r="K16">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="L16">
         <v>5</v>
@@ -9120,13 +9114,13 @@
         <v>75</v>
       </c>
       <c r="T16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U16" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V16" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W16">
         <v>0.1667</v>
@@ -9216,10 +9210,10 @@
         <v>91.40000000000001</v>
       </c>
       <c r="AZ16" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA16" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB16">
         <v>88.5</v>
@@ -9306,7 +9300,7 @@
         <v>1.1862</v>
       </c>
       <c r="CD16" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE16">
         <v>956</v>
@@ -9389,25 +9383,25 @@
         <v>122</v>
       </c>
       <c r="E17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G17" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H17" t="s">
         <v>199</v>
       </c>
       <c r="I17" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="J17">
-        <v>166.5</v>
+        <v>173.8</v>
       </c>
       <c r="K17">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L17">
         <v>5</v>
@@ -9434,13 +9428,13 @@
         <v>75</v>
       </c>
       <c r="T17" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U17" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V17" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W17">
         <v>0.1667</v>
@@ -9530,10 +9524,10 @@
         <v>91.8</v>
       </c>
       <c r="AZ17" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA17" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB17">
         <v>86.2</v>
@@ -9620,7 +9614,7 @@
         <v>1.1921</v>
       </c>
       <c r="CD17" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE17">
         <v>770</v>
@@ -9703,25 +9697,25 @@
         <v>123</v>
       </c>
       <c r="E18" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F18" t="s">
         <v>111</v>
       </c>
       <c r="G18" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H18" t="s">
         <v>200</v>
       </c>
       <c r="I18" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J18">
-        <v>299.7</v>
+        <v>307</v>
       </c>
       <c r="K18">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -9748,13 +9742,13 @@
         <v>100</v>
       </c>
       <c r="T18" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U18" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="V18" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="W18">
         <v>0.1667</v>
@@ -9844,10 +9838,10 @@
         <v>166.8</v>
       </c>
       <c r="AZ18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="BA18" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="BB18">
         <v>93</v>
@@ -9934,7 +9928,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD18" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE18">
         <v>858</v>
@@ -10017,25 +10011,25 @@
         <v>123</v>
       </c>
       <c r="E19" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F19" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H19" t="s">
         <v>200</v>
       </c>
       <c r="I19" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J19">
-        <v>299.7</v>
+        <v>307</v>
       </c>
       <c r="K19">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="L19">
         <v>5</v>
@@ -10062,13 +10056,13 @@
         <v>75</v>
       </c>
       <c r="T19" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U19" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="V19" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="W19">
         <v>0.1667</v>
@@ -10158,10 +10152,10 @@
         <v>176.1</v>
       </c>
       <c r="AZ19" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA19" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB19">
         <v>89.8</v>
@@ -10248,7 +10242,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD19" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE19">
         <v>858</v>
@@ -10331,25 +10325,25 @@
         <v>123</v>
       </c>
       <c r="E20" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F20" t="s">
         <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H20" t="s">
         <v>200</v>
       </c>
       <c r="I20" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J20">
-        <v>299.7</v>
+        <v>307</v>
       </c>
       <c r="K20">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="L20">
         <v>5</v>
@@ -10376,13 +10370,13 @@
         <v>18.8</v>
       </c>
       <c r="T20" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U20" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V20" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W20">
         <v>0.1667</v>
@@ -10409,7 +10403,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE20" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="AF20">
         <v>85</v>
@@ -10472,10 +10466,10 @@
         <v>235.5</v>
       </c>
       <c r="AZ20" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA20" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB20">
         <v>54.6</v>
@@ -10562,7 +10556,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE20">
         <v>858</v>
@@ -10645,25 +10639,25 @@
         <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F21" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G21" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H21" t="s">
         <v>200</v>
       </c>
       <c r="I21" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="J21">
-        <v>299.7</v>
+        <v>307</v>
       </c>
       <c r="K21">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -10690,13 +10684,13 @@
         <v>18.8</v>
       </c>
       <c r="T21" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U21" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V21" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W21">
         <v>0.1667</v>
@@ -10723,7 +10717,7 @@
         <v>-0.2</v>
       </c>
       <c r="AE21" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="AF21">
         <v>82.5</v>
@@ -10786,10 +10780,10 @@
         <v>262.6</v>
       </c>
       <c r="AZ21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BA21" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BB21">
         <v>22.4</v>
@@ -10876,7 +10870,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD21" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE21">
         <v>858</v>
@@ -10959,25 +10953,25 @@
         <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F22" t="s">
         <v>112</v>
       </c>
       <c r="G22" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H22" t="s">
         <v>201</v>
       </c>
       <c r="I22" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J22">
-        <v>293.2</v>
+        <v>300.4</v>
       </c>
       <c r="K22">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="L22">
         <v>5</v>
@@ -11004,13 +10998,13 @@
         <v>56.2</v>
       </c>
       <c r="T22" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U22" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V22" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W22">
         <v>0.0833</v>
@@ -11019,7 +11013,7 @@
         <v>6.4</v>
       </c>
       <c r="Y22">
-        <v>93.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="Z22">
         <v>55.1</v>
@@ -11100,10 +11094,10 @@
         <v>87.59999999999999</v>
       </c>
       <c r="AZ22" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA22" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB22">
         <v>89.3</v>
@@ -11190,7 +11184,7 @@
         <v>1.1664</v>
       </c>
       <c r="CD22" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE22">
         <v>1553</v>
@@ -11273,25 +11267,25 @@
         <v>124</v>
       </c>
       <c r="E23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F23" t="s">
         <v>115</v>
       </c>
       <c r="G23" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H23" t="s">
         <v>201</v>
       </c>
       <c r="I23" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J23">
-        <v>293.2</v>
+        <v>300.4</v>
       </c>
       <c r="K23">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L23">
         <v>5</v>
@@ -11318,13 +11312,13 @@
         <v>75</v>
       </c>
       <c r="T23" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U23" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V23" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W23">
         <v>0.0833</v>
@@ -11414,10 +11408,10 @@
         <v>85.5</v>
       </c>
       <c r="AZ23" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA23" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB23">
         <v>88.2</v>
@@ -11504,7 +11498,7 @@
         <v>1.1714</v>
       </c>
       <c r="CD23" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE23">
         <v>1404</v>
@@ -11587,25 +11581,25 @@
         <v>124</v>
       </c>
       <c r="E24" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F24" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G24" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H24" t="s">
         <v>201</v>
       </c>
       <c r="I24" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J24">
-        <v>293.2</v>
+        <v>300.4</v>
       </c>
       <c r="K24">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="L24">
         <v>5</v>
@@ -11632,13 +11626,13 @@
         <v>56.2</v>
       </c>
       <c r="T24" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U24" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V24" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W24">
         <v>0.0833</v>
@@ -11728,10 +11722,10 @@
         <v>86.90000000000001</v>
       </c>
       <c r="AZ24" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA24" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB24">
         <v>87.3</v>
@@ -11818,7 +11812,7 @@
         <v>1.1794</v>
       </c>
       <c r="CD24" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE24">
         <v>1152</v>
@@ -11901,25 +11895,25 @@
         <v>124</v>
       </c>
       <c r="E25" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F25" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G25" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H25" t="s">
         <v>201</v>
       </c>
       <c r="I25" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="J25">
-        <v>293.2</v>
+        <v>300.4</v>
       </c>
       <c r="K25">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="L25">
         <v>5</v>
@@ -11946,13 +11940,13 @@
         <v>56.2</v>
       </c>
       <c r="T25" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U25" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V25" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W25">
         <v>0.0833</v>
@@ -12042,10 +12036,10 @@
         <v>90</v>
       </c>
       <c r="AZ25" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA25" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB25">
         <v>89.8</v>
@@ -12132,7 +12126,7 @@
         <v>1.1854</v>
       </c>
       <c r="CD25" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE25">
         <v>961</v>
@@ -12215,25 +12209,25 @@
         <v>125</v>
       </c>
       <c r="E26" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F26" t="s">
         <v>113</v>
       </c>
       <c r="G26" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H26" t="s">
         <v>202</v>
       </c>
       <c r="I26" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J26">
-        <v>376</v>
+        <v>383.2</v>
       </c>
       <c r="K26">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="L26">
         <v>5</v>
@@ -12260,13 +12254,13 @@
         <v>0</v>
       </c>
       <c r="T26" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U26" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V26" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W26">
         <v>0.1667</v>
@@ -12356,10 +12350,10 @@
         <v>288.9</v>
       </c>
       <c r="AZ26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="BA26" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="BB26">
         <v>97.7</v>
@@ -12446,7 +12440,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD26" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE26">
         <v>858</v>
@@ -12529,25 +12523,25 @@
         <v>125</v>
       </c>
       <c r="E27" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F27" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G27" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H27" t="s">
         <v>202</v>
       </c>
       <c r="I27" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J27">
-        <v>376</v>
+        <v>383.2</v>
       </c>
       <c r="K27">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L27">
         <v>5</v>
@@ -12574,13 +12568,13 @@
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U27" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V27" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W27">
         <v>0.1667</v>
@@ -12607,7 +12601,7 @@
         <v>0</v>
       </c>
       <c r="AE27" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="AF27">
         <v>87.8</v>
@@ -12670,10 +12664,10 @@
         <v>297.8</v>
       </c>
       <c r="AZ27" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="BA27" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="BB27">
         <v>97.90000000000001</v>
@@ -12760,7 +12754,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD27" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE27">
         <v>858</v>
@@ -12843,25 +12837,25 @@
         <v>125</v>
       </c>
       <c r="E28" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="G28" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H28" t="s">
         <v>202</v>
       </c>
       <c r="I28" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J28">
-        <v>376</v>
+        <v>383.2</v>
       </c>
       <c r="K28">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="L28">
         <v>5</v>
@@ -12888,13 +12882,13 @@
         <v>0</v>
       </c>
       <c r="T28" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U28" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V28" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W28">
         <v>0.1667</v>
@@ -12921,7 +12915,7 @@
         <v>0</v>
       </c>
       <c r="AE28" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AF28">
         <v>85.59999999999999</v>
@@ -12984,10 +12978,10 @@
         <v>299</v>
       </c>
       <c r="AZ28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="BA28" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="BB28">
         <v>95</v>
@@ -13074,7 +13068,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD28" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE28">
         <v>858</v>
@@ -13157,25 +13151,25 @@
         <v>125</v>
       </c>
       <c r="E29" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F29" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="G29" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H29" t="s">
         <v>202</v>
       </c>
       <c r="I29" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="J29">
-        <v>376</v>
+        <v>383.2</v>
       </c>
       <c r="K29">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="L29">
         <v>5</v>
@@ -13202,13 +13196,13 @@
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U29" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V29" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W29">
         <v>0.1667</v>
@@ -13298,10 +13292,10 @@
         <v>300.2</v>
       </c>
       <c r="AZ29" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="BA29" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="BB29">
         <v>83.8</v>
@@ -13388,7 +13382,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD29" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE29">
         <v>858</v>
@@ -13471,25 +13465,25 @@
         <v>126</v>
       </c>
       <c r="E30" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F30" t="s">
         <v>114</v>
       </c>
       <c r="G30" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H30" t="s">
         <v>203</v>
       </c>
       <c r="I30" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J30">
-        <v>150.5</v>
+        <v>157.7</v>
       </c>
       <c r="K30">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="L30">
         <v>5</v>
@@ -13516,13 +13510,13 @@
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U30" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V30" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W30">
         <v>0.6667</v>
@@ -13612,10 +13606,10 @@
         <v>269</v>
       </c>
       <c r="AZ30" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BA30" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BB30">
         <v>75.7</v>
@@ -13702,7 +13696,7 @@
         <v>1.1321</v>
       </c>
       <c r="CD30" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE30">
         <v>2463</v>
@@ -13785,25 +13779,25 @@
         <v>126</v>
       </c>
       <c r="E31" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F31" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="G31" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H31" t="s">
         <v>203</v>
       </c>
       <c r="I31" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J31">
-        <v>150.5</v>
+        <v>157.7</v>
       </c>
       <c r="K31">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -13830,13 +13824,13 @@
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U31" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V31" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W31">
         <v>0.6667</v>
@@ -13926,10 +13920,10 @@
         <v>260</v>
       </c>
       <c r="AZ31" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BA31" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BB31">
         <v>61.7</v>
@@ -14016,7 +14010,7 @@
         <v>1.1359</v>
       </c>
       <c r="CD31" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE31">
         <v>2353</v>
@@ -14099,25 +14093,25 @@
         <v>126</v>
       </c>
       <c r="E32" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F32" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="G32" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H32" t="s">
         <v>203</v>
       </c>
       <c r="I32" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J32">
-        <v>150.5</v>
+        <v>157.7</v>
       </c>
       <c r="K32">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="L32">
         <v>5</v>
@@ -14144,13 +14138,13 @@
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U32" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V32" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W32">
         <v>0.6667</v>
@@ -14240,10 +14234,10 @@
         <v>230.3</v>
       </c>
       <c r="AZ32" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="BA32" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="BB32">
         <v>50.5</v>
@@ -14330,7 +14324,7 @@
         <v>1.1434</v>
       </c>
       <c r="CD32" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE32">
         <v>2125</v>
@@ -14413,25 +14407,25 @@
         <v>126</v>
       </c>
       <c r="E33" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F33" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="G33" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H33" t="s">
         <v>203</v>
       </c>
       <c r="I33" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="J33">
-        <v>150.5</v>
+        <v>157.7</v>
       </c>
       <c r="K33">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="L33">
         <v>5</v>
@@ -14458,13 +14452,13 @@
         <v>56.2</v>
       </c>
       <c r="T33" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U33" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V33" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W33">
         <v>0.6667</v>
@@ -14554,10 +14548,10 @@
         <v>172.8</v>
       </c>
       <c r="AZ33" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BA33" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BB33">
         <v>20.2</v>
@@ -14644,7 +14638,7 @@
         <v>1.1491</v>
       </c>
       <c r="CD33" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE33">
         <v>1950</v>
@@ -14695,7 +14689,7 @@
         <v>193</v>
       </c>
       <c r="CU33">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CV33" t="s">
         <v>193</v>
@@ -14727,25 +14721,25 @@
         <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F34" t="s">
         <v>115</v>
       </c>
       <c r="G34" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H34" t="s">
         <v>204</v>
       </c>
       <c r="I34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J34">
-        <v>84.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="K34">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -14772,13 +14766,13 @@
         <v>0</v>
       </c>
       <c r="T34" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U34" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V34" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W34">
         <v>0.0833</v>
@@ -14868,10 +14862,10 @@
         <v>99.90000000000001</v>
       </c>
       <c r="AZ34" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA34" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB34">
         <v>97.40000000000001</v>
@@ -14958,7 +14952,7 @@
         <v>1.1682</v>
       </c>
       <c r="CD34" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE34">
         <v>1479</v>
@@ -15009,7 +15003,7 @@
         <v>193</v>
       </c>
       <c r="CU34">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CV34" t="s">
         <v>193</v>
@@ -15041,25 +15035,25 @@
         <v>127</v>
       </c>
       <c r="E35" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F35" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G35" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H35" t="s">
         <v>204</v>
       </c>
       <c r="I35" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J35">
-        <v>84.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="K35">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="L35">
         <v>5</v>
@@ -15086,13 +15080,13 @@
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U35" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V35" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W35">
         <v>0.0833</v>
@@ -15176,16 +15170,16 @@
         <v>4.1</v>
       </c>
       <c r="AX35" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AY35">
         <v>103</v>
       </c>
       <c r="AZ35" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA35" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB35">
         <v>87.90000000000001</v>
@@ -15272,7 +15266,7 @@
         <v>1.1727</v>
       </c>
       <c r="CD35" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE35">
         <v>1331</v>
@@ -15355,25 +15349,25 @@
         <v>127</v>
       </c>
       <c r="E36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F36" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="G36" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H36" t="s">
         <v>204</v>
       </c>
       <c r="I36" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J36">
-        <v>84.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="K36">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="L36">
         <v>5</v>
@@ -15400,13 +15394,13 @@
         <v>56.2</v>
       </c>
       <c r="T36" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U36" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V36" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W36">
         <v>0.0833</v>
@@ -15496,10 +15490,10 @@
         <v>97.90000000000001</v>
       </c>
       <c r="AZ36" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA36" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB36">
         <v>77.09999999999999</v>
@@ -15586,7 +15580,7 @@
         <v>1.1776</v>
       </c>
       <c r="CD36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE36">
         <v>1170</v>
@@ -15669,25 +15663,25 @@
         <v>127</v>
       </c>
       <c r="E37" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F37" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="G37" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H37" t="s">
         <v>204</v>
       </c>
       <c r="I37" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="J37">
-        <v>84.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="K37">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="L37">
         <v>5</v>
@@ -15714,13 +15708,13 @@
         <v>0</v>
       </c>
       <c r="T37" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U37" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="V37" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="W37">
         <v>0.0833</v>
@@ -15804,16 +15798,16 @@
         <v>7.7</v>
       </c>
       <c r="AX37" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AY37">
         <v>119.3</v>
       </c>
       <c r="AZ37" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA37" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB37">
         <v>73.8</v>
@@ -15900,7 +15894,7 @@
         <v>1.1808</v>
       </c>
       <c r="CD37" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE37">
         <v>1061</v>
@@ -15983,25 +15977,25 @@
         <v>128</v>
       </c>
       <c r="E38" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F38" t="s">
         <v>116</v>
       </c>
       <c r="G38" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H38" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I38" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J38">
-        <v>101</v>
+        <v>108.3</v>
       </c>
       <c r="K38">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L38">
         <v>5</v>
@@ -16028,13 +16022,13 @@
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U38" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V38" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W38">
         <v>0.1667</v>
@@ -16124,10 +16118,10 @@
         <v>286.7</v>
       </c>
       <c r="AZ38" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="BA38" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="BB38">
         <v>88.7</v>
@@ -16214,7 +16208,7 @@
         <v>1.0981</v>
       </c>
       <c r="CD38" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="CE38">
         <v>3534</v>
@@ -16265,7 +16259,7 @@
         <v>193</v>
       </c>
       <c r="CU38">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CV38" t="s">
         <v>193</v>
@@ -16297,25 +16291,25 @@
         <v>128</v>
       </c>
       <c r="E39" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F39" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G39" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H39" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I39" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J39">
-        <v>101</v>
+        <v>108.3</v>
       </c>
       <c r="K39">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="L39">
         <v>5</v>
@@ -16342,13 +16336,13 @@
         <v>0</v>
       </c>
       <c r="T39" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U39" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V39" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W39">
         <v>0.1667</v>
@@ -16438,10 +16432,10 @@
         <v>269.4</v>
       </c>
       <c r="AZ39" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BA39" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="BB39">
         <v>66.8</v>
@@ -16528,7 +16522,7 @@
         <v>1.1001</v>
       </c>
       <c r="CD39" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE39">
         <v>3470</v>
@@ -16611,25 +16605,25 @@
         <v>128</v>
       </c>
       <c r="E40" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F40" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G40" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I40" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J40">
-        <v>101</v>
+        <v>108.3</v>
       </c>
       <c r="K40">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -16656,13 +16650,13 @@
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U40" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V40" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W40">
         <v>0.1667</v>
@@ -16752,10 +16746,10 @@
         <v>251</v>
       </c>
       <c r="AZ40" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BA40" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BB40">
         <v>66</v>
@@ -16842,7 +16836,7 @@
         <v>1.1037</v>
       </c>
       <c r="CD40" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE40">
         <v>3343</v>
@@ -16893,7 +16887,7 @@
         <v>193</v>
       </c>
       <c r="CU40">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="CV40" t="s">
         <v>193</v>
@@ -16925,25 +16919,25 @@
         <v>128</v>
       </c>
       <c r="E41" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F41" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G41" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H41" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I41" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="J41">
-        <v>101</v>
+        <v>108.3</v>
       </c>
       <c r="K41">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="L41">
         <v>5</v>
@@ -16970,13 +16964,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U41" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V41" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W41">
         <v>0.1667</v>
@@ -17066,10 +17060,10 @@
         <v>232.4</v>
       </c>
       <c r="AZ41" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BA41" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BB41">
         <v>63.4</v>
@@ -17156,7 +17150,7 @@
         <v>1.1126</v>
       </c>
       <c r="CD41" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE41">
         <v>3045</v>
@@ -17239,25 +17233,25 @@
         <v>129</v>
       </c>
       <c r="E42" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F42" t="s">
         <v>116</v>
       </c>
       <c r="G42" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H42" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I42" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J42">
-        <v>331</v>
+        <v>338.2</v>
       </c>
       <c r="K42">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L42">
         <v>5</v>
@@ -17284,13 +17278,13 @@
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U42" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V42" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W42">
         <v>0.1667</v>
@@ -17380,10 +17374,10 @@
         <v>229.8</v>
       </c>
       <c r="AZ42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA42" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB42">
         <v>96.59999999999999</v>
@@ -17470,7 +17464,7 @@
         <v>1.1402</v>
       </c>
       <c r="CD42" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE42">
         <v>2185</v>
@@ -17553,25 +17547,25 @@
         <v>129</v>
       </c>
       <c r="E43" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F43" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G43" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H43" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I43" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J43">
-        <v>331</v>
+        <v>338.2</v>
       </c>
       <c r="K43">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="L43">
         <v>5</v>
@@ -17598,13 +17592,13 @@
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U43" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V43" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W43">
         <v>0.1667</v>
@@ -17694,10 +17688,10 @@
         <v>227.8</v>
       </c>
       <c r="AZ43" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA43" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB43">
         <v>95.40000000000001</v>
@@ -17784,7 +17778,7 @@
         <v>1.1411</v>
       </c>
       <c r="CD43" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE43">
         <v>2151</v>
@@ -17867,25 +17861,25 @@
         <v>129</v>
       </c>
       <c r="E44" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G44" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I44" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J44">
-        <v>331</v>
+        <v>338.2</v>
       </c>
       <c r="K44">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="L44">
         <v>5</v>
@@ -17912,13 +17906,13 @@
         <v>0</v>
       </c>
       <c r="T44" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U44" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V44" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W44">
         <v>0.1667</v>
@@ -18008,10 +18002,10 @@
         <v>219.2</v>
       </c>
       <c r="AZ44" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA44" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB44">
         <v>92.59999999999999</v>
@@ -18098,7 +18092,7 @@
         <v>1.1444</v>
       </c>
       <c r="CD44" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE44">
         <v>2048</v>
@@ -18181,25 +18175,25 @@
         <v>129</v>
       </c>
       <c r="E45" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F45" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G45" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H45" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I45" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="J45">
-        <v>331</v>
+        <v>338.2</v>
       </c>
       <c r="K45">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="L45">
         <v>5</v>
@@ -18226,13 +18220,13 @@
         <v>56.2</v>
       </c>
       <c r="T45" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U45" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V45" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W45">
         <v>0.1667</v>
@@ -18322,10 +18316,10 @@
         <v>198.6</v>
       </c>
       <c r="AZ45" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA45" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB45">
         <v>83.3</v>
@@ -18412,7 +18406,7 @@
         <v>1.1441</v>
       </c>
       <c r="CD45" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE45">
         <v>2050</v>
@@ -18495,25 +18489,25 @@
         <v>130</v>
       </c>
       <c r="E46" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F46" t="s">
         <v>116</v>
       </c>
       <c r="G46" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I46" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J46">
-        <v>95.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="K46">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="L46">
         <v>5</v>
@@ -18540,13 +18534,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U46" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V46" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W46">
         <v>0.1667</v>
@@ -18636,10 +18630,10 @@
         <v>235.1</v>
       </c>
       <c r="AZ46" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA46" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB46">
         <v>89.8</v>
@@ -18726,7 +18720,7 @@
         <v>1.1299</v>
       </c>
       <c r="CD46" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE46">
         <v>2507</v>
@@ -18777,7 +18771,7 @@
         <v>193</v>
       </c>
       <c r="CU46">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="CV46" t="s">
         <v>193</v>
@@ -18809,25 +18803,25 @@
         <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F47" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="G47" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H47" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I47" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J47">
-        <v>95.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="K47">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="L47">
         <v>5</v>
@@ -18854,13 +18848,13 @@
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U47" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V47" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W47">
         <v>0.1667</v>
@@ -18950,10 +18944,10 @@
         <v>235.1</v>
       </c>
       <c r="AZ47" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA47" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB47">
         <v>93.90000000000001</v>
@@ -19040,7 +19034,7 @@
         <v>1.1306</v>
       </c>
       <c r="CD47" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE47">
         <v>2485</v>
@@ -19123,25 +19117,25 @@
         <v>130</v>
       </c>
       <c r="E48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G48" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H48" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I48" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J48">
-        <v>95.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="K48">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="L48">
         <v>5</v>
@@ -19168,13 +19162,13 @@
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U48" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V48" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W48">
         <v>0.1667</v>
@@ -19264,10 +19258,10 @@
         <v>219.9</v>
       </c>
       <c r="AZ48" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA48" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB48">
         <v>89.5</v>
@@ -19354,7 +19348,7 @@
         <v>1.1344</v>
       </c>
       <c r="CD48" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE48">
         <v>2366</v>
@@ -19437,25 +19431,25 @@
         <v>130</v>
       </c>
       <c r="E49" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G49" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H49" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I49" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="J49">
-        <v>95.59999999999999</v>
+        <v>102.8</v>
       </c>
       <c r="K49">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="L49">
         <v>5</v>
@@ -19482,13 +19476,13 @@
         <v>56.2</v>
       </c>
       <c r="T49" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U49" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V49" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W49">
         <v>0.1667</v>
@@ -19578,10 +19572,10 @@
         <v>206.6</v>
       </c>
       <c r="AZ49" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA49" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB49">
         <v>86.8</v>
@@ -19668,7 +19662,7 @@
         <v>1.1405</v>
       </c>
       <c r="CD49" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE49">
         <v>2170</v>
@@ -19751,25 +19745,25 @@
         <v>131</v>
       </c>
       <c r="E50" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F50" t="s">
         <v>117</v>
       </c>
       <c r="G50" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I50" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J50">
-        <v>387.3</v>
+        <v>394.5</v>
       </c>
       <c r="K50">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="L50">
         <v>5</v>
@@ -19796,13 +19790,13 @@
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U50" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V50" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W50">
         <v>0.25</v>
@@ -19892,10 +19886,10 @@
         <v>123.8</v>
       </c>
       <c r="AZ50" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA50" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB50">
         <v>90.5</v>
@@ -19982,7 +19976,7 @@
         <v>1.1795</v>
       </c>
       <c r="CD50" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE50">
         <v>1157</v>
@@ -20065,25 +20059,25 @@
         <v>131</v>
       </c>
       <c r="E51" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F51" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G51" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H51" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I51" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J51">
-        <v>387.3</v>
+        <v>394.5</v>
       </c>
       <c r="K51">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L51">
         <v>5</v>
@@ -20110,13 +20104,13 @@
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U51" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V51" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W51">
         <v>0.25</v>
@@ -20206,10 +20200,10 @@
         <v>125</v>
       </c>
       <c r="AZ51" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="BA51" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="BB51">
         <v>90.90000000000001</v>
@@ -20296,7 +20290,7 @@
         <v>1.1876</v>
       </c>
       <c r="CD51" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE51">
         <v>907</v>
@@ -20379,25 +20373,25 @@
         <v>131</v>
       </c>
       <c r="E52" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F52" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G52" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H52" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I52" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J52">
-        <v>387.3</v>
+        <v>394.5</v>
       </c>
       <c r="K52">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="L52">
         <v>5</v>
@@ -20424,13 +20418,13 @@
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U52" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V52" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W52">
         <v>0.25</v>
@@ -20514,16 +20508,16 @@
         <v>7.7</v>
       </c>
       <c r="AX52" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AY52">
         <v>123.6</v>
       </c>
       <c r="AZ52" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA52" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB52">
         <v>90.90000000000001</v>
@@ -20610,7 +20604,7 @@
         <v>1.1936</v>
       </c>
       <c r="CD52" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE52">
         <v>726</v>
@@ -20693,25 +20687,25 @@
         <v>131</v>
       </c>
       <c r="E53" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F53" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G53" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="H53" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I53" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="J53">
-        <v>387.3</v>
+        <v>394.5</v>
       </c>
       <c r="K53">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="L53">
         <v>5</v>
@@ -20738,13 +20732,13 @@
         <v>0</v>
       </c>
       <c r="T53" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U53" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="V53" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="W53">
         <v>0.25</v>
@@ -20828,16 +20822,16 @@
         <v>8.300000000000001</v>
       </c>
       <c r="AX53" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AY53">
         <v>121.1</v>
       </c>
       <c r="AZ53" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA53" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB53">
         <v>73.2</v>
@@ -20924,7 +20918,7 @@
         <v>1.1969</v>
       </c>
       <c r="CD53" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE53">
         <v>624</v>
@@ -21007,25 +21001,25 @@
         <v>132</v>
       </c>
       <c r="E54" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F54" t="s">
         <v>118</v>
       </c>
       <c r="G54" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H54" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I54" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J54">
-        <v>36.2</v>
+        <v>43.4</v>
       </c>
       <c r="K54">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="L54">
         <v>5</v>
@@ -21052,13 +21046,13 @@
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U54" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V54" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W54">
         <v>0.25</v>
@@ -21148,10 +21142,10 @@
         <v>212</v>
       </c>
       <c r="AZ54" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BA54" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BB54">
         <v>33.1</v>
@@ -21238,7 +21232,7 @@
         <v>1.1284</v>
       </c>
       <c r="CD54" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE54">
         <v>2482</v>
@@ -21321,25 +21315,25 @@
         <v>132</v>
       </c>
       <c r="E55" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F55" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G55" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H55" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I55" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J55">
-        <v>36.2</v>
+        <v>43.4</v>
       </c>
       <c r="K55">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L55">
         <v>5</v>
@@ -21366,13 +21360,13 @@
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U55" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V55" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W55">
         <v>0.25</v>
@@ -21399,7 +21393,7 @@
         <v>0.3</v>
       </c>
       <c r="AE55" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AF55">
         <v>87.7</v>
@@ -21462,10 +21456,10 @@
         <v>148.5</v>
       </c>
       <c r="AZ55" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BA55" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BB55">
         <v>30.6</v>
@@ -21552,7 +21546,7 @@
         <v>1.1302</v>
       </c>
       <c r="CD55" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE55">
         <v>2429</v>
@@ -21635,25 +21629,25 @@
         <v>132</v>
       </c>
       <c r="E56" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F56" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G56" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I56" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J56">
-        <v>36.2</v>
+        <v>43.4</v>
       </c>
       <c r="K56">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="L56">
         <v>5</v>
@@ -21680,13 +21674,13 @@
         <v>56.2</v>
       </c>
       <c r="T56" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U56" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V56" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W56">
         <v>0.25</v>
@@ -21770,16 +21764,16 @@
         <v>4.2</v>
       </c>
       <c r="AX56" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="AY56">
         <v>103.1</v>
       </c>
       <c r="AZ56" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BA56" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="BB56">
         <v>27.1</v>
@@ -21866,7 +21860,7 @@
         <v>1.1345</v>
       </c>
       <c r="CD56" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE56">
         <v>2284</v>
@@ -21949,25 +21943,25 @@
         <v>132</v>
       </c>
       <c r="E57" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F57" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G57" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="H57" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I57" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="J57">
-        <v>36.2</v>
+        <v>43.4</v>
       </c>
       <c r="K57">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="L57">
         <v>5</v>
@@ -21994,13 +21988,13 @@
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U57" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V57" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W57">
         <v>0.25</v>
@@ -22090,10 +22084,10 @@
         <v>142.5</v>
       </c>
       <c r="AZ57" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BA57" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="BB57">
         <v>68.5</v>
@@ -22180,7 +22174,7 @@
         <v>1.1434</v>
       </c>
       <c r="CD57" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="CE57">
         <v>2004</v>
@@ -22231,7 +22225,7 @@
         <v>193</v>
       </c>
       <c r="CU57">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="CV57" t="s">
         <v>193</v>
@@ -22263,25 +22257,25 @@
         <v>133</v>
       </c>
       <c r="E58" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F58" t="s">
         <v>118</v>
       </c>
       <c r="G58" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H58" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I58" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J58">
-        <v>125.4</v>
+        <v>132.6</v>
       </c>
       <c r="K58">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="L58">
         <v>5</v>
@@ -22308,13 +22302,13 @@
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U58" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="V58" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="W58">
         <v>0.25</v>
@@ -22404,10 +22398,10 @@
         <v>181</v>
       </c>
       <c r="AZ58" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BA58" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BB58">
         <v>92.90000000000001</v>
@@ -22494,7 +22488,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD58" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE58">
         <v>858</v>
@@ -22577,25 +22571,25 @@
         <v>133</v>
       </c>
       <c r="E59" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F59" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G59" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H59" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I59" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J59">
-        <v>125.4</v>
+        <v>132.6</v>
       </c>
       <c r="K59">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="L59">
         <v>5</v>
@@ -22622,13 +22616,13 @@
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U59" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="V59" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="W59">
         <v>0.25</v>
@@ -22718,10 +22712,10 @@
         <v>178.8</v>
       </c>
       <c r="AZ59" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BA59" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BB59">
         <v>93.09999999999999</v>
@@ -22808,7 +22802,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD59" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE59">
         <v>858</v>
@@ -22891,25 +22885,25 @@
         <v>133</v>
       </c>
       <c r="E60" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F60" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G60" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H60" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I60" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J60">
-        <v>125.4</v>
+        <v>132.6</v>
       </c>
       <c r="K60">
-        <v>24</v>
+        <v>23.8</v>
       </c>
       <c r="L60">
         <v>5</v>
@@ -22936,13 +22930,13 @@
         <v>0</v>
       </c>
       <c r="T60" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U60" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V60" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="W60">
         <v>0.25</v>
@@ -23032,10 +23026,10 @@
         <v>177.8</v>
       </c>
       <c r="AZ60" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BA60" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BB60">
         <v>95.3</v>
@@ -23122,7 +23116,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD60" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE60">
         <v>858</v>
@@ -23205,25 +23199,25 @@
         <v>133</v>
       </c>
       <c r="E61" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F61" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G61" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="H61" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I61" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="J61">
-        <v>125.4</v>
+        <v>132.6</v>
       </c>
       <c r="K61">
-        <v>25</v>
+        <v>24.8</v>
       </c>
       <c r="L61">
         <v>5</v>
@@ -23250,13 +23244,13 @@
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U61" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="V61" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="W61">
         <v>0.25</v>
@@ -23346,10 +23340,10 @@
         <v>176.9</v>
       </c>
       <c r="AZ61" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BA61" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="BB61">
         <v>95.40000000000001</v>
@@ -23436,7 +23430,7 @@
         <v>1.1896</v>
       </c>
       <c r="CD61" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="CE61">
         <v>858</v>
